--- a/Decisions/CHURN/CHTR Rec1 Attribution Dashboard.xlsx
+++ b/Decisions/CHURN/CHTR Rec1 Attribution Dashboard.xlsx
@@ -31,20 +31,20 @@
     <definedName name="Param_CMCSA_On">Parameters!$C$18</definedName>
     <definedName name="Param_InputMode">Parameters!$C$19</definedName>
     <definedName name="Param_CommitExcess">Parameters!$C$22</definedName>
-    <definedName name="Dash_Print">Dashboard!$C$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Dashboard'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$N$58</definedName>
+    <definedName name="Dash_Print">Dashboard!$B$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Dashboard'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$N$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Cover'!$A$1:$B$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net-loss tracker'!$A$5:$P$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Net-loss tracker'!$A$1:$P$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Attribution'!$A$1:$P$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Segments'!$A$1:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Net-loss tracker'!$A$5:$P$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Net-loss tracker'!$A$1:$P$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Attribution'!$A$1:$P$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Segments'!$A$1:$P$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Parameters'!$A$1:$F$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Assumptions'!$A$5:$G$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Assumptions'!$A$1:$G$80</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Playbook'!$A$1:$G$20</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" calcOnSave="1"/>
 </workbook>
 </file>
 
@@ -284,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -325,13 +325,6 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -343,6 +336,11 @@
       <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -502,13 +500,6 @@
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
-    <title>
-      <tx>
-        <strRef>
-          <f>'Dashboard'!$B$18</f>
-        </strRef>
-      </tx>
-    </title>
     <plotArea>
       <barChart>
         <barDir val="bar"/>
@@ -533,13 +524,13 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'Dashboard'!$B$20:$B$26</f>
-            </numRef>
+            <strRef>
+              <f>'Dashboard'!$B$20:$B$25</f>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$20:$E$26</f>
+              <f>'Dashboard'!$E$20:$E$25</f>
             </numRef>
           </val>
         </ser>
@@ -563,13 +554,13 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'Dashboard'!$B$20:$B$26</f>
-            </numRef>
+            <strRef>
+              <f>'Dashboard'!$B$20:$B$25</f>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$20:$F$26</f>
+              <f>'Dashboard'!$F$20:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -581,144 +572,10 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <numFmt formatCode="@" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <strRef>
-          <f>'Dashboard'!$B$29</f>
-        </strRef>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!B31</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$C$30:$N$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$C$31:$N$31</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!B32</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A6A6A6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="A6A6A6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="A6A6A6"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$C$30:$N$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$C$32:$N$32</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -731,6 +588,7 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
+        <numFmt formatCode="@" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -754,7 +612,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2880000"/>
+    <ext cx="4320000" cy="1800000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -764,28 +622,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1084,11 +920,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:N58"/>
+  <dimension ref="B1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1116,11 +952,14 @@
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
-      <c r="J1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="B2" s="4">
-        <f>IF(C15="","Fill the quarterly net-loss tracker first — attribution cells are empty on purpose.",C15)</f>
+        <f>IF(C15="","Public prints are retrieved. Attribution / disconnect sample is empty — the playbook does not fire.",C15)</f>
         <v/>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1135,10 +974,11 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="3" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="5">
-        <f>CONCATENATE("Selected: ",Parameters!C5,"   ·   Units: residential Internet customers   ·   "&amp;"Yellow INPUT on Net-loss tracker / Attribution / Segments   ·   "&amp;"Public spine: Ex99.1 Q1 2026 res. Internet −117,000 · Q2 2026 −166,000 (RETRIEVED)   ·   "&amp;"Template — not a filled mix")</f>
-        <v/>
+    <row r="3" ht="36" customHeight="1">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>This sheet is OUTPUT (locked). Paste yellow INPUT on: Net-loss tracker E7 (T2 gross) / E8 (T3 disconnects); Attribution E6 (A1–A6 counts); Segments E7 (WHERE). Public spine: Q1 2026 res. Internet -117,000 · Q2 2026 -166,000 (RETRIEVED). GAP R1–R4 fires only from sampled COUNTS — not from |print|.</t>
+        </is>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
@@ -1176,7 +1016,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Largest reason</t>
+          <t>Largest mapped reason</t>
         </is>
       </c>
       <c r="L5" s="2" t="n"/>
@@ -1196,13 +1036,13 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="7">
-        <f>IF(OR(Parameters!C18="No",'Net-loss tracker'!B46=""),"n/a",'Net-loss tracker'!B46)</f>
+        <f>IF(Parameters!C18="No","n/a",IF(Parameters!C5="Q1 2026",Parameters!C22,IF('Net-loss tracker'!B46="","n/a",'Net-loss tracker'!B46)))</f>
         <v/>
       </c>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="8">
-        <f>IF(Attribution!C49="No","EMPTY",Attribution!D48)</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),"EMPTY",IF(Attribution!C51="HOLD","HOLD — residual",Attribution!D48))</f>
         <v/>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -1222,13 +1062,13 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="5">
-        <f>"Q1 playbook commit 54k"</f>
+        <f>"unallocated until first fill — not a cell in the mix"</f>
         <v/>
       </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="5">
-        <f>IF(Attribution!C49="No","do not fire a play",TEXT(Attribution!C48,"0% of disconnects"))</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),"do not fire a play",IF(Attribution!C51="HOLD","sample incomplete",TEXT(Attribution!C48,"0% of T3")))</f>
         <v/>
       </c>
       <c r="L7" s="2" t="n"/>
@@ -1278,7 +1118,7 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="3" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="B11" s="11" t="inlineStr">
         <is>
           <t>G1 tracker</t>
@@ -1302,14 +1142,14 @@
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="3" t="n"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="28" customHeight="1">
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dominant driver (pptx &gt;= P4)</t>
+          <t>Dominant mapped driver (A1–A6 only)</t>
         </is>
       </c>
       <c r="C12" s="12">
-        <f>IF(Attribution!C49="No","EMPTY — no reason fill",IF(Attribution!C48&gt;=Parameters!C8,"DOMINANT — "&amp;Attribution!D48&amp;" holds "&amp;TEXT(Attribution!C48,"0%")&amp;" (&gt;= "&amp;TEXT(Parameters!C8,"0%")&amp;")",IF(Attribution!C48&gt;=Parameters!C9,"MIXED — largest is "&amp;TEXT(Attribution!C48,"0%")&amp;" (25-40% band). Run top two as experiments.","NULL — no cohort &gt;= "&amp;TEXT(Parameters!C9,"0%")&amp;". Scenario 6 fires.")))</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),"EMPTY — no sampled mix",IF(Attribution!C51="HOLD","HOLD — residual is largest or material. Sample incomplete.",IF(Attribution!C48&gt;=Parameters!C8,"DOMINANT — "&amp;Attribution!D48&amp;" holds "&amp;TEXT(Attribution!C48,"0%")&amp;" (&gt;= "&amp;TEXT(Parameters!C8,"0%")&amp;")",IF(Attribution!C48&gt;=Parameters!C9,"MIXED — largest is "&amp;TEXT(Attribution!C48,"0%")&amp;". Run top two as experiments.","NULL — no GAP branch &gt;= "&amp;TEXT(Parameters!C9,"0%")&amp;"."))))</f>
         <v/>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -1320,16 +1160,16 @@
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="13">
-        <f>IF(Attribution!C49="No","EMPTY",IF(Attribution!C48&gt;=Parameters!C8,"RED — fire one play",IF(Attribution!C48&gt;=Parameters!C9,"AMBER — experiment","GREEN — null / S6")))</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),"EMPTY",IF(Attribution!C51="HOLD","HOLD — residual",IF(AND(Attribution!C48&gt;=Parameters!C8,N(Attribution!C52)&gt;=Parameters!C8,Parameters!C16="Yes"),"RED — full-scale armed",IF(Attribution!C48&gt;=Parameters!C8,"AMBER — experiment only",IF(Attribution!C48&gt;=Parameters!C9,"AMBER — mixed experiment","GREEN — no branch")))))</f>
         <v/>
       </c>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="3" t="n"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="28" customHeight="1">
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Scenario routed</t>
+          <t>GAP branch routed</t>
         </is>
       </c>
       <c r="C13" s="12">
@@ -1344,13 +1184,13 @@
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="13">
-        <f>IF(Attribution!C49="No","HOLD","SEE PLAYBOOK")</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48="",Attribution!C51="HOLD"),"HOLD","SEE R1–R4")</f>
         <v/>
       </c>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="3" t="n"/>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="B14" s="11" t="inlineStr">
         <is>
           <t>WHERE / WHO flag</t>
@@ -1381,7 +1221,7 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>IF(Attribution!C49="No","Fill the quarterly net-loss tracker first — attribution cells are empty on purpose.",IF(Attribution!C48&gt;=Parameters!C8,Attribution!D48&amp;" accounts for "&amp;TEXT(Attribution!C48,"0%")&amp;" of disconnects — above the "&amp;TEXT(Parameters!C8,"0%")&amp;" dominant-driver gate. Fire that one play on the core.",IF(Attribution!C48&gt;=Parameters!C9,"Mixed picture: "&amp;Attribution!D48&amp;" is largest at "&amp;TEXT(Attribution!C48,"0%")&amp;" but below "&amp;TEXT(Parameters!C8,"0%")&amp;". Run the top two as controlled experiments.","No dominant driver — no cohort reaches "&amp;TEXT(Parameters!C9,"0%")&amp;" of disconnects. Scenario 6 (null) is the recommendation, not a guess.")))</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),"Public prints are retrieved. Attribution / disconnect sample is empty — the playbook does not fire.",IF(Attribution!C51="HOLD","Sample incomplete — residual is largest or material (≥2% of T3). Do not fire a reason play.",IF(Attribution!C48&gt;=Parameters!C8,Attribution!D48&amp;" accounts for "&amp;TEXT(Attribution!C48,"0%")&amp;" of sampled disconnects — above the "&amp;TEXT(Parameters!C8,"0%")&amp;" dominant-driver gate."&amp;IF(LEFT(Segments!C79,4)="Core"," Fire that GAP branch on the core — do not add rural miles.",IF(LEFT(Segments!C79,5)="Rural"," Fire on rural Internet already passed — not more miles (W2).",IF(LEFT(Segments!C79,5)="EMPTY"," WHERE untested — do not pick miles vs core yet."," Read F2 before picking geography."))),IF(Attribution!C48&gt;=Parameters!C9,"Mixed picture: "&amp;Attribution!D48&amp;" is largest at "&amp;TEXT(Attribution!C48,"0%")&amp;" but below "&amp;TEXT(Parameters!C8,"0%")&amp;". Run the top two as controlled experiments.","No GAP branch reaches "&amp;TEXT(Parameters!C9,"0%")&amp;" of disconnects. Disclose and experiment — do not fire an expensive lever."))))</f>
         <v/>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -1402,7 +1242,7 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>IF(Attribution!C49="No","HOLD — empty cells. The playbook does not fire.",IF(AND(INDEX(Attribution!D40:D45,1)&gt;=Parameters!C10,N(Segments!D71)&gt;=0.3),"S1 FWA-driven — convergence pricing in FWA zones (kill: no churn split in 2 qtrs / negative bundle margin)",IF(INDEX(Attribution!D40:D45,2)&gt;=Parameters!C11,"S2 Fiber-driven — re-sequence evolution on overlap + symmetric win-back (kill: completed zones bleed at same rate)",IF(INDEX(Attribution!D40:D45,3)&gt;=Parameters!C12,"S3 Satellite-driven — accelerate rural activation (kill: new-passing penetration below underwriting)",IF(INDEX(Attribution!D40:D45,4)&gt;=Parameters!C9,"S4 Housing / move-out — mover capture, not a save-offer (kill: port-out data contradicts the macro story)",IF(INDEX(Attribution!D40:D45,5)&gt;=Parameters!C9,"S5 Non-pay — value tier at delinquency (kill: save-rate economics below LTV)",IF(Attribution!C48&lt;Parameters!C9,"S6 Null — no dominant driver. Market-layer disclosure + spend-capped experiments.","Largest cell is "&amp;Attribution!D48&amp;" — apply the matching lead play; do not fire two expensive levers."))))))</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48="",Attribution!C51="HOLD"),"HOLD — empty or incomplete sample. GAP R1–R4 does not fire.",IF(Attribution!D48=Parameters!B29,"R1 Move-out — TOS/MDU / instant-on for 6 months. Cheaper lever first. Not a save-offer.",IF(Attribution!D48=Parameters!B26,"R2 FWA — 12-month rate-lock on and off overlap; hand on-overlap FWA to fiber if it is a stepping-stone.",IF(AND(Attribution!D48=Parameters!B27,N(Segments!D55)+N(Segments!D56)&gt;=0.5),"R3 Fiber — overlap zips concentrate losses. Gig/symmetry there; node-split only if the sample names speed.",IF(Attribution!D48=Parameters!B27,"R3 Fiber — overlap WHERE untested or rest-of-footprint. Do not fire company-wide rebuild off-overlap (W4).",IF(Attribution!D48=Parameters!B30,"R4 Nonpay — payment arrangement / 90-day first-bill save.",IF(Attribution!D48=Parameters!B28,"HOLD — satellite is a WHERE overlay (W2), not a GAP spend program.",IF(Attribution!C48&lt;Parameters!C9,"No GAP branch clears the mixed floor. Disclose and experiment; do not fire an expensive lever.","Largest mapped cell is "&amp;Attribution!D48&amp;" — that GAP branch only; never two expensive levers."))))))))</f>
         <v/>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1418,7 +1258,7 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="4">
-        <f>IF(Attribution!C49="No","Reason contribution is empty — fill Attribution before this chart can make a claim","Largest leak is "&amp;Attribution!D48&amp;" at "&amp;TEXT(Attribution!C48,"0%")&amp;" of sampled disconnects  ·  gray = the rest  ·  accent = the story bar")</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),"No reason chart until a sampled mix and T3 base exist (empty is not seven zeros)",IF(Attribution!C51="HOLD","HOLD — residual is material. Bars omitted until the sample reconciles.","Largest mapped leak is "&amp;Attribution!D48&amp;" at "&amp;TEXT(Attribution!C48,"0%")&amp;" of T3  ·  gray = the rest  ·  accent = the story bar"))</f>
         <v/>
       </c>
       <c r="C18" s="2" t="n"/>
@@ -1436,7 +1276,7 @@
     <row r="19">
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Reason (sorted)</t>
+          <t>Reason (A1–A6 sorted)</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1462,726 +1302,526 @@
     </row>
     <row r="20">
       <c r="B20" s="12">
-        <f>Attribution!B54</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!B56)</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>Attribution!C54</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!C56)</f>
         <v/>
       </c>
       <c r="D20" s="15">
-        <f>Attribution!D54</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!D56)</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>Attribution!E54</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!E56)</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>Attribution!F54</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!F56)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="12">
-        <f>Attribution!B55</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!B57)</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f>Attribution!C55</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!C57)</f>
         <v/>
       </c>
       <c r="D21" s="15">
-        <f>Attribution!D55</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!D57)</f>
         <v/>
       </c>
       <c r="E21" s="14">
-        <f>Attribution!E55</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!E57)</f>
         <v/>
       </c>
       <c r="F21" s="14">
-        <f>Attribution!F55</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!F57)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="12">
-        <f>Attribution!B56</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!B58)</f>
         <v/>
       </c>
       <c r="C22" s="14">
-        <f>Attribution!C56</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!C58)</f>
         <v/>
       </c>
       <c r="D22" s="15">
-        <f>Attribution!D56</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!D58)</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>Attribution!E56</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!E58)</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>Attribution!F56</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!F58)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="12">
-        <f>Attribution!B57</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!B59)</f>
         <v/>
       </c>
       <c r="C23" s="14">
-        <f>Attribution!C57</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!C59)</f>
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>Attribution!D57</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!D59)</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f>Attribution!E57</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!E59)</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>Attribution!F57</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!F59)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="12">
-        <f>Attribution!B58</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!B60)</f>
         <v/>
       </c>
       <c r="C24" s="14">
-        <f>Attribution!C58</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!C60)</f>
         <v/>
       </c>
       <c r="D24" s="15">
-        <f>Attribution!D58</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!D60)</f>
         <v/>
       </c>
       <c r="E24" s="14">
-        <f>Attribution!E58</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!E60)</f>
         <v/>
       </c>
       <c r="F24" s="14">
-        <f>Attribution!F58</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!F60)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="12">
-        <f>Attribution!B59</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!B61)</f>
         <v/>
       </c>
       <c r="C25" s="14">
-        <f>Attribution!C59</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!C61)</f>
         <v/>
       </c>
       <c r="D25" s="15">
-        <f>Attribution!D59</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!D61)</f>
         <v/>
       </c>
       <c r="E25" s="14">
-        <f>Attribution!E59</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!E61)</f>
         <v/>
       </c>
       <c r="F25" s="14">
-        <f>Attribution!F59</f>
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),NA(),Attribution!F61)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="12">
-        <f>Attribution!B60</f>
-        <v/>
-      </c>
-      <c r="C26" s="14">
-        <f>Attribution!C60</f>
-        <v/>
-      </c>
-      <c r="D26" s="15">
-        <f>Attribution!D60</f>
-        <v/>
-      </c>
-      <c r="E26" s="14">
-        <f>Attribution!E60</f>
-        <v/>
-      </c>
-      <c r="F26" s="14">
-        <f>Attribution!F60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Source: Attribution A1-A7 (user-entered counts) · Residual is derived · Bars begin at zero · One accent (largest) vs gray · Not a pie</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="4">
-        <f>IF('Net-loss tracker'!J11="","Residential Internet print — public spine only until internals fill","Charter residential Internet stayed worse than Comcast in every quarter both prints exist")</f>
-        <v/>
-      </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="3" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Source: Attribution A1–A6 sampled counts only · Residual is a FLAG, never a story bar · NA() until C49=Yes and T3 exists · Bars begin at zero · One accent vs gray · Not a pie</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Quarter</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Q1 2024</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Q2 2024</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Q3 2024</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Q4 2024</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Q1 2025</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>Q3 2025</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>Q4 2025</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>Q1 2026</t>
-        </is>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>CHTR res. Internet</t>
-        </is>
-      </c>
-      <c r="C31" s="14">
-        <f>IF('Net-loss tracker'!E11="",NA(),'Net-loss tracker'!E11)</f>
-        <v/>
-      </c>
-      <c r="D31" s="14">
-        <f>IF('Net-loss tracker'!F11="",NA(),'Net-loss tracker'!F11)</f>
-        <v/>
-      </c>
-      <c r="E31" s="14">
-        <f>IF('Net-loss tracker'!G11="",NA(),'Net-loss tracker'!G11)</f>
-        <v/>
-      </c>
-      <c r="F31" s="14">
-        <f>IF('Net-loss tracker'!H11="",NA(),'Net-loss tracker'!H11)</f>
-        <v/>
-      </c>
-      <c r="G31" s="14">
-        <f>IF('Net-loss tracker'!I11="",NA(),'Net-loss tracker'!I11)</f>
-        <v/>
-      </c>
-      <c r="H31" s="14">
-        <f>IF('Net-loss tracker'!J11="",NA(),'Net-loss tracker'!J11)</f>
-        <v/>
-      </c>
-      <c r="I31" s="14">
-        <f>IF('Net-loss tracker'!K11="",NA(),'Net-loss tracker'!K11)</f>
-        <v/>
-      </c>
-      <c r="J31" s="14">
-        <f>IF('Net-loss tracker'!L11="",NA(),'Net-loss tracker'!L11)</f>
-        <v/>
-      </c>
-      <c r="K31" s="14">
-        <f>IF('Net-loss tracker'!M11="",NA(),'Net-loss tracker'!M11)</f>
-        <v/>
-      </c>
-      <c r="L31" s="14">
-        <f>IF('Net-loss tracker'!N11="",NA(),'Net-loss tracker'!N11)</f>
-        <v/>
-      </c>
-      <c r="M31" s="14">
-        <f>IF('Net-loss tracker'!O11="",NA(),'Net-loss tracker'!O11)</f>
-        <v/>
-      </c>
-      <c r="N31" s="14">
-        <f>IF('Net-loss tracker'!P11="",NA(),'Net-loss tracker'!P11)</f>
-        <v/>
-      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>APPENDIX  ·  peer overlap (not a second exhibit) and kill rules</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="3" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="B31" s="4">
+        <f>IF(SUM('Net-loss tracker'!E56:P56)=0,"No overlapping CHTR/CMCSA print — do not claim a multi-quarter peer gap.",IF(SUM('Net-loss tracker'!E56:P56)=1,INDEX('Net-loss tracker'!E5:P5,MATCH(1,'Net-loss tracker'!E56:P56,0))&amp;": CHTR "&amp;TEXT(INDEX('Net-loss tracker'!E11:P11,MATCH(1,'Net-loss tracker'!E56:P56,0)),"#,##0;(#,##0)")&amp;" vs CMCSA "&amp;TEXT(INDEX('Net-loss tracker'!E14:P14,MATCH(1,'Net-loss tracker'!E56:P56,0)),"#,##0;(#,##0)")&amp;" (only quarter both prints exist).","CHTR vs CMCSA overlap exists in "&amp;TEXT(SUM('Net-loss tracker'!E56:P56),"0")&amp;" quarters. Not a filled mix — see Net-loss tracker."))</f>
+        <v/>
+      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>CMCSA resid. BB</t>
-        </is>
-      </c>
-      <c r="C32" s="14">
-        <f>IF('Net-loss tracker'!E14="",NA(),'Net-loss tracker'!E14)</f>
-        <v/>
-      </c>
-      <c r="D32" s="14">
-        <f>IF('Net-loss tracker'!F14="",NA(),'Net-loss tracker'!F14)</f>
-        <v/>
-      </c>
-      <c r="E32" s="14">
-        <f>IF('Net-loss tracker'!G14="",NA(),'Net-loss tracker'!G14)</f>
-        <v/>
-      </c>
-      <c r="F32" s="14">
-        <f>IF('Net-loss tracker'!H14="",NA(),'Net-loss tracker'!H14)</f>
-        <v/>
-      </c>
-      <c r="G32" s="14">
-        <f>IF('Net-loss tracker'!I14="",NA(),'Net-loss tracker'!I14)</f>
-        <v/>
-      </c>
-      <c r="H32" s="14">
-        <f>IF('Net-loss tracker'!J14="",NA(),'Net-loss tracker'!J14)</f>
-        <v/>
-      </c>
-      <c r="I32" s="14">
-        <f>IF('Net-loss tracker'!K14="",NA(),'Net-loss tracker'!K14)</f>
-        <v/>
-      </c>
-      <c r="J32" s="14">
-        <f>IF('Net-loss tracker'!L14="",NA(),'Net-loss tracker'!L14)</f>
-        <v/>
-      </c>
-      <c r="K32" s="14">
-        <f>IF('Net-loss tracker'!M14="",NA(),'Net-loss tracker'!M14)</f>
-        <v/>
-      </c>
-      <c r="L32" s="14">
-        <f>IF('Net-loss tracker'!N14="",NA(),'Net-loss tracker'!N14)</f>
-        <v/>
-      </c>
-      <c r="M32" s="14">
-        <f>IF('Net-loss tracker'!O14="",NA(),'Net-loss tracker'!O14)</f>
-        <v/>
-      </c>
-      <c r="N32" s="14">
-        <f>IF('Net-loss tracker'!P14="",NA(),'Net-loss tracker'!P14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Excess vs CMCSA rate</t>
-        </is>
-      </c>
-      <c r="C33" s="14">
-        <f>IF('Net-loss tracker'!E20="",NA(),'Net-loss tracker'!E20)</f>
-        <v/>
-      </c>
-      <c r="D33" s="14">
-        <f>IF('Net-loss tracker'!F20="",NA(),'Net-loss tracker'!F20)</f>
-        <v/>
-      </c>
-      <c r="E33" s="14">
-        <f>IF('Net-loss tracker'!G20="",NA(),'Net-loss tracker'!G20)</f>
-        <v/>
-      </c>
-      <c r="F33" s="14">
-        <f>IF('Net-loss tracker'!H20="",NA(),'Net-loss tracker'!H20)</f>
-        <v/>
-      </c>
-      <c r="G33" s="14">
-        <f>IF('Net-loss tracker'!I20="",NA(),'Net-loss tracker'!I20)</f>
-        <v/>
-      </c>
-      <c r="H33" s="14">
-        <f>IF('Net-loss tracker'!J20="",NA(),'Net-loss tracker'!J20)</f>
-        <v/>
-      </c>
-      <c r="I33" s="14">
-        <f>IF('Net-loss tracker'!K20="",NA(),'Net-loss tracker'!K20)</f>
-        <v/>
-      </c>
-      <c r="J33" s="14">
-        <f>IF('Net-loss tracker'!L20="",NA(),'Net-loss tracker'!L20)</f>
-        <v/>
-      </c>
-      <c r="K33" s="14">
-        <f>IF('Net-loss tracker'!M20="",NA(),'Net-loss tracker'!M20)</f>
-        <v/>
-      </c>
-      <c r="L33" s="14">
-        <f>IF('Net-loss tracker'!N20="",NA(),'Net-loss tracker'!N20)</f>
-        <v/>
-      </c>
-      <c r="M33" s="14">
-        <f>IF('Net-loss tracker'!O20="",NA(),'Net-loss tracker'!O20)</f>
-        <v/>
-      </c>
-      <c r="N33" s="14">
-        <f>IF('Net-loss tracker'!P20="",NA(),'Net-loss tracker'!P20)</f>
-        <v/>
-      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>No second chart on this sheet. The exhibit above is the reason bars (or a blank plot with NA gaps when EMPTY).</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Axis note: line chart may zoom off zero because the story is movement in a tight negative band. Bars on this sheet still start at zero.</t>
-        </is>
-      </c>
-      <c r="L34" s="16" t="n"/>
-      <c r="M34" s="17" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>APPENDIX  ·  kill rules (not the exhibit)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="K35" s="18" t="n"/>
-      <c r="M35" s="19" t="n"/>
-    </row>
-    <row r="36">
-      <c r="K36" s="20" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="22" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>KILL RULES AND UNWILLING-TO-CLAIM  ·  written before the recommendation</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
-      <c r="M48" s="3" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>Rule (from pptx + six-recommendation-areas / decisions.md)</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Rule (GAP / six-recommendation-areas / decisions.md)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>This quarter</t>
         </is>
       </c>
-      <c r="L49" s="2" t="n"/>
-      <c r="M49" s="3" t="n"/>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="B50" s="11" t="inlineStr">
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="3" t="n"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Tracker already exists and is used quarterly -&gt; skip Area 1 build; go to mix control.</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="13">
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="13">
         <f>IF(LEFT(Parameters!C17,3)="Yes","KILL — skip G1 build","OPEN — fill G1")</f>
         <v/>
       </c>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="3" t="n"/>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="B51" s="11" t="inlineStr">
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="3" t="n"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>K2</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Fill shows move-out matching Comcast -&gt; kill Area 2 as a Charter-specific print; Area 6 becomes the CEO-charge answer. Do not add rural miles.</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="13">
-        <f>IF(OR(Attribution!C49="No",'Net-loss tracker'!B46=""),"UNTESTED",IF(AND(Attribution!D48=Parameters!B29,'Net-loss tracker'!B46&lt;=0),"KILL Area 2 — move-out / no excess","OPEN")</f>
-        <v/>
-      </c>
-      <c r="L51" s="2" t="n"/>
-      <c r="M51" s="3" t="n"/>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="B52" s="11" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Fill shows move-out matching Comcast -&gt; kill Area 2 as a Charter-specific print. Do not add rural miles.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="13">
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C51="HOLD",'Net-loss tracker'!B46=""),"UNTESTED",IF(AND(Attribution!D48=Parameters!B29,N('Net-loss tracker'!B46)&lt;=0),"KILL Area 2 — move-out / no excess","OPEN"))</f>
+        <v/>
+      </c>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>K3</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Do not fire two expensive levers in the same quarter. Co-equal cells: cheaper first (Parameters P9).</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="13">
-        <f>IF(AND(Attribution!C49="Yes",Attribution!C50&gt;=Parameters!C9,ABS(Attribution!C48-Attribution!C50)&lt;=Parameters!C13),"CO-EQUAL — fire the cheaper lever only","OK")</f>
-        <v/>
-      </c>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="3" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="B53" s="11" t="inlineStr">
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="13">
+        <f>IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C51="HOLD"),"OK",IF(AND(N(Attribution!C50)&gt;=Parameters!C9,ABS(N(Attribution!C48)-N(Attribution!C50))&lt;=Parameters!C13),"CO-EQUAL — fire the cheaper lever only","OK"))</f>
+        <v/>
+      </c>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="3" t="n"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>K4</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Do not treat call-center reason codes as the trigger. Sample the disconnect (pptx slide 4).</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="13" t="inlineStr">
         <is>
           <t>PROCESS — not a cell</t>
         </is>
       </c>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="3" t="n"/>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="B54" s="11" t="inlineStr">
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="3" t="n"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>K5</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Do not add rural miles to fix a core leak. Do not fire company-wide upgrade/rebuild as the default to move-out, FWA, nonpay, or off-overlap.</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="13">
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="13">
         <f>IF(LEFT(Segments!C79,4)="Core","CORE — no rural miles",IF(LEFT(Segments!C78,5)="EMPTY","UNTESTED","READ F2"))</f>
         <v/>
       </c>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="3" t="n"/>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="B55" s="11" t="inlineStr">
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="3" t="n"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>K6</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>PPTX interlock: two consecutive quarters before full-scale (experiments may start on one).</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="13">
-        <f>IF(Parameters!C16="Yes","ARMED — full-scale needs 2 qtrs","OFF")</f>
-        <v/>
-      </c>
-      <c r="L55" s="2" t="n"/>
-      <c r="M55" s="3" t="n"/>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="B56" s="11" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Two consecutive quarters over the dominant gate before full-scale; experiments may start on one.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="13">
+        <f>IF(Parameters!C16&lt;&gt;"Yes","OFF — two-quarter interlock not required",IF(OR(Attribution!C49&lt;&gt;"Yes",Attribution!C48=""),"UNTESTED — no mix this quarter",IF(OR(Attribution!C51="HOLD",Attribution!C52=""),"EXPERIMENT ONLY — prior empty or residual HOLD; full-scale not armed",IF(AND(Attribution!C48&gt;=Parameters!C8,Attribution!C52&gt;=Parameters!C8),"FULL-SCALE armed — two consecutive quarters over P4","EXPERIMENT ONLY — needs two consecutive quarters over P4"))))</f>
+        <v/>
+      </c>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>K7</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Unwilling to claim: a filled mix, a gross churn rate, that -66k re-rates five-year ~80%, that mobile offsets Internet, that 54k sits in any one cell until the first fill.</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="13" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Unwilling to claim: a filled mix, a gross churn rate, that -66k re-rates five-year ~80%, that 54k sits in any one cell until the first fill.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="13" t="inlineStr">
         <is>
           <t>STANDING</t>
         </is>
       </c>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="3" t="n"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Print-friendly: this sheet is the exhibit. Backup arithmetic lives on Net-loss tracker, Attribution, Segments, Assumptions. Do not present empty attribution cells as a measured mix. Title (row 2) updates from formulas when numbers are pasted.</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="3" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="3" t="n"/>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Do not credit mobile / video against this residential Internet print.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>STANDING</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Exhibit is rows 1–27 (one takeaway + one chart). Kill rules are appendix. Backup arithmetic: Net-loss tracker, Attribution, Segments, Assumptions. Do not present empty attribution cells as a measured mix.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="3" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="50">
+  <mergeCells count="53">
     <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B48:M48"/>
-    <mergeCell ref="K50:M50"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="K40:M40"/>
     <mergeCell ref="C15:M15"/>
-    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="C42:J42"/>
     <mergeCell ref="C14:J14"/>
+    <mergeCell ref="B1:M1"/>
     <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="C37:J37"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B29:M29"/>
-    <mergeCell ref="C49:J49"/>
+    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="B34:M34"/>
+    <mergeCell ref="K42:M42"/>
     <mergeCell ref="K14:M14"/>
     <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C54:J54"/>
-    <mergeCell ref="C50:J50"/>
+    <mergeCell ref="K39:M39"/>
     <mergeCell ref="C16:M16"/>
+    <mergeCell ref="C41:J41"/>
     <mergeCell ref="B9:M9"/>
-    <mergeCell ref="C55:J55"/>
+    <mergeCell ref="B30:M30"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="C40:J40"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="C56:J56"/>
+    <mergeCell ref="K38:M38"/>
     <mergeCell ref="K10:M10"/>
+    <mergeCell ref="C43:J43"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="K13:M13"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="C11:J11"/>
-    <mergeCell ref="C51:J51"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="C52:J52"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="B45:M45"/>
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="B26:M26"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="K34:M36"/>
+    <mergeCell ref="C39:J39"/>
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="K5:M5"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="K55:M55"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="B31:M31"/>
+    <mergeCell ref="C38:J38"/>
+    <mergeCell ref="K35:M35"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="B18:M18"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="C53:J53"/>
-    <mergeCell ref="B58:M58"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="H6:J6"/>
   </mergeCells>
@@ -2201,17 +1841,20 @@
     <cfRule type="expression" priority="5" dxfId="2">
       <formula>LEFT(K11,4)="SKIP"</formula>
     </cfRule>
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>LEFT(K11,4)="HOLD"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K50:M56">
-    <cfRule type="expression" priority="6" dxfId="1">
-      <formula>LEFT(K50,4)="KILL"</formula>
+  <conditionalFormatting sqref="K36:M43">
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>LEFT(K36,4)="KILL"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="0">
-      <formula>LEFT(K50,4)="OPEN"</formula>
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>LEFT(K36,4)="OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1" horizontalDpi="300"/>
+  <pageSetup orientation="landscape" paperSize="3" fitToHeight="0" fitToWidth="1" horizontalDpi="300"/>
   <headerFooter>
     <oddHeader>&amp;LCHTR Rec 1 · Attribution diagnostic TEMPLATE</oddHeader>
     <oddFooter>&amp;LYellow = INPUT · Green = RETRIEVED Ex99.1 · Gray = formula · Not a filled mix&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -2220,6 +1863,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="28" min="0" max="16383" man="1"/>
+  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2270,7 +1916,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Rec 1 sensor + playbook from CHTR_Rec1_AttributionPlaybook.pptx, wired to the G1 quarterly net-loss tracker language in Decisions/six-recommendation-areas.md and Decisions/decisions.md. Charter (or the case team) pastes internals; Excel diagnoses them.</t>
+          <t>Rec 1 G1 tracker + GAP R1–R4 reason play from Decisions/six-recommendation-areas.md and Decisions/decisions.md. The pptx is the Playbook leave-behind (reference only). Dashboard does not fire S1–S6. Charter (or the case team) pastes internals; Excel diagnoses them.</t>
         </is>
       </c>
     </row>
@@ -2295,7 +1941,7 @@
       <c r="B8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Yellow + blue font</t>
         </is>
@@ -2307,7 +1953,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2319,7 +1965,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Blue fill</t>
         </is>
@@ -2406,7 +2052,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Row 2 is the takeaway (formula). Traffic lights apply pptx 40 / 25 / 35 gates. One accent bar vs gray. Kill rules sit on the same page. If Attribution is empty, the title will tell you to fill the tracker first — believe it.</t>
+          <t>Row 2 is the takeaway (formula). Lights apply GAP R1–R4. Residual cannot fire. Paste start cells: tracker E7/E8, Attribution E6, Segments E7. If Attribution is empty, the title says the sample is empty while public −117k/−166k stay labeled RETRIEVED — believe it.</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2669,31 +2315,31 @@
           <t>six-recommendation-areas.md: “Fill the quarterly net-loss tracker first.” Unit = residential Internet. Prefer gross adds vs disconnects so net is a formula. Yellow = Charter internals (INPUT). Green = public Ex99.1 / trending (RETRIEVED). Do not treat rural CR +41k / +47k as this Internet cut. Do not fire a reason play from empty cells.</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="16" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="17" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n"/>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="n"/>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="21" t="n"/>
-      <c r="I3" s="21" t="n"/>
-      <c r="J3" s="21" t="n"/>
-      <c r="K3" s="21" t="n"/>
-      <c r="L3" s="22" t="n"/>
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="23" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
@@ -2798,38 +2444,38 @@
           <t>Prior-quarter EOP. Prefill = trending identity (RETRIEVED). Overwrite if internal census differs.</t>
         </is>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="24" t="n">
         <v>28544000</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="24" t="n">
         <v>28472000</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="24" t="n">
         <v>28318000</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="24" t="n">
         <v>28205000</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="24" t="n">
         <v>28034000</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="24" t="n">
         <v>27979000</v>
       </c>
-      <c r="K6" s="26" t="n">
+      <c r="K6" s="24" t="n">
         <v>27868000</v>
       </c>
-      <c r="L6" s="26" t="n">
+      <c r="L6" s="24" t="n">
         <v>27760000</v>
       </c>
-      <c r="M6" s="26" t="n">
+      <c r="M6" s="24" t="n">
         <v>27641000</v>
       </c>
-      <c r="N6" s="26" t="n">
+      <c r="N6" s="24" t="n">
         <v>27524000</v>
       </c>
-      <c r="O6" s="27" t="n"/>
-      <c r="P6" s="27" t="n"/>
+      <c r="O6" s="25" t="n"/>
+      <c r="P6" s="25" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -2852,18 +2498,18 @@
           <t>Not disclosed. Leave blank until the tracker exists. Sampled, not a guess.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="25" t="n"/>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="25" t="n"/>
+      <c r="L7" s="25" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="25" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -2886,18 +2532,18 @@
           <t>Not disclosed. Sample the disconnect — do not paste agent codes as the file (pptx slide 4).</t>
         </is>
       </c>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="27" t="n"/>
-      <c r="O8" s="27" t="n"/>
-      <c r="P8" s="27" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="L8" s="25" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="25" t="n"/>
+      <c r="O8" s="25" t="n"/>
+      <c r="P8" s="25" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -2920,51 +2566,51 @@
           <t>Blank until both T2 and T3 are filled. Zero is not a fill.</t>
         </is>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="26">
         <f>IF(OR(E7="",E8=""),"",E7-E8)</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="26">
         <f>IF(OR(F7="",F8=""),"",F7-F8)</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="26">
         <f>IF(OR(G7="",G8=""),"",G7-G8)</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="26">
         <f>IF(OR(H7="",H8=""),"",H7-H8)</f>
         <v/>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="26">
         <f>IF(OR(I7="",I8=""),"",I7-I8)</f>
         <v/>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="26">
         <f>IF(OR(J7="",J8=""),"",J7-J8)</f>
         <v/>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="26">
         <f>IF(OR(K7="",K8=""),"",K7-K8)</f>
         <v/>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="26">
         <f>IF(OR(L7="",L8=""),"",L7-L8)</f>
         <v/>
       </c>
-      <c r="M9" s="28">
+      <c r="M9" s="26">
         <f>IF(OR(M7="",M8=""),"",M7-M8)</f>
         <v/>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="26">
         <f>IF(OR(N7="",N8=""),"",N7-N8)</f>
         <v/>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="26">
         <f>IF(OR(O7="",O8=""),"",O7-O8)</f>
         <v/>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="26">
         <f>IF(OR(P7="",P8=""),"",P7-P8)</f>
         <v/>
       </c>
@@ -2990,38 +2636,38 @@
           <t>CHTR Ex99.1 / Q1 trending. Q1 2026 = −117,000. Q2 2026 = −166,000. FY columns omitted.</t>
         </is>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="24" t="n">
         <v>-72000</v>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="24" t="n">
         <v>-154000</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="24" t="n">
         <v>-113000</v>
       </c>
-      <c r="H10" s="26" t="n">
+      <c r="H10" s="24" t="n">
         <v>-171000</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="24" t="n">
         <v>-55000</v>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="24" t="n">
         <v>-111000</v>
       </c>
-      <c r="K10" s="26" t="n">
+      <c r="K10" s="24" t="n">
         <v>-108000</v>
       </c>
-      <c r="L10" s="26" t="n">
+      <c r="L10" s="24" t="n">
         <v>-119000</v>
       </c>
-      <c r="M10" s="26" t="n">
+      <c r="M10" s="24" t="n">
         <v>-117000</v>
       </c>
-      <c r="N10" s="26" t="n">
+      <c r="N10" s="24" t="n">
         <v>-166000</v>
       </c>
-      <c r="O10" s="27" t="n"/>
-      <c r="P10" s="27" t="n"/>
+      <c r="O10" s="25" t="n"/>
+      <c r="P10" s="25" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -3044,51 +2690,51 @@
           <t>Internal net if T2 and T3 filled; else public print. Never invent a mix on top of this.</t>
         </is>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="26">
         <f>IF(E9&lt;&gt;"",E9,IF(E10&lt;&gt;"",E10,""))</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="26">
         <f>IF(F9&lt;&gt;"",F9,IF(F10&lt;&gt;"",F10,""))</f>
         <v/>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="26">
         <f>IF(G9&lt;&gt;"",G9,IF(G10&lt;&gt;"",G10,""))</f>
         <v/>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="26">
         <f>IF(H9&lt;&gt;"",H9,IF(H10&lt;&gt;"",H10,""))</f>
         <v/>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="26">
         <f>IF(I9&lt;&gt;"",I9,IF(I10&lt;&gt;"",I10,""))</f>
         <v/>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="26">
         <f>IF(J9&lt;&gt;"",J9,IF(J10&lt;&gt;"",J10,""))</f>
         <v/>
       </c>
-      <c r="K11" s="28">
+      <c r="K11" s="26">
         <f>IF(K9&lt;&gt;"",K9,IF(K10&lt;&gt;"",K10,""))</f>
         <v/>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="26">
         <f>IF(L9&lt;&gt;"",L9,IF(L10&lt;&gt;"",L10,""))</f>
         <v/>
       </c>
-      <c r="M11" s="28">
+      <c r="M11" s="26">
         <f>IF(M9&lt;&gt;"",M9,IF(M10&lt;&gt;"",M10,""))</f>
         <v/>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="26">
         <f>IF(N9&lt;&gt;"",N9,IF(N10&lt;&gt;"",N10,""))</f>
         <v/>
       </c>
-      <c r="O11" s="28">
+      <c r="O11" s="26">
         <f>IF(O9&lt;&gt;"",O9,IF(O10&lt;&gt;"",O10,""))</f>
         <v/>
       </c>
-      <c r="P11" s="28">
+      <c r="P11" s="26">
         <f>IF(P9&lt;&gt;"",P9,IF(P10&lt;&gt;"",P10,""))</f>
         <v/>
       </c>
@@ -3114,38 +2760,38 @@
           <t>Ex99.1 total Internet. Q1 2026 −120,000 · Q2 2026 −172,000. Includes SMB.</t>
         </is>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="27" t="n">
         <v>-72000</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="27" t="n">
         <v>-148000</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="27" t="n">
         <v>-110000</v>
       </c>
-      <c r="H12" s="29" t="n">
+      <c r="H12" s="27" t="n">
         <v>-177000</v>
       </c>
-      <c r="I12" s="29" t="n">
+      <c r="I12" s="27" t="n">
         <v>-59000</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="27" t="n">
         <v>-116000</v>
       </c>
-      <c r="K12" s="29" t="n">
+      <c r="K12" s="27" t="n">
         <v>-109000</v>
       </c>
-      <c r="L12" s="29" t="n">
+      <c r="L12" s="27" t="n">
         <v>-119000</v>
       </c>
-      <c r="M12" s="29" t="n">
+      <c r="M12" s="27" t="n">
         <v>-120000</v>
       </c>
-      <c r="N12" s="29" t="n">
+      <c r="N12" s="27" t="n">
         <v>-172000</v>
       </c>
-      <c r="O12" s="27" t="n"/>
-      <c r="P12" s="27" t="n"/>
+      <c r="O12" s="25" t="n"/>
+      <c r="P12" s="25" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -3168,22 +2814,22 @@
           <t>Ex99.1 rural-footprint customer relationships. Q1 +41,000 · Q2 +47,000. Do not use as T6.</t>
         </is>
       </c>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="27" t="n"/>
-      <c r="H13" s="27" t="n"/>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="29" t="n">
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="25" t="n"/>
+      <c r="M13" s="27" t="n">
         <v>41000</v>
       </c>
-      <c r="N13" s="29" t="n">
+      <c r="N13" s="27" t="n">
         <v>47000</v>
       </c>
-      <c r="O13" s="27" t="n"/>
-      <c r="P13" s="27" t="n"/>
+      <c r="O13" s="25" t="n"/>
+      <c r="P13" s="25" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -3206,20 +2852,20 @@
           <t>Q1 2026 −65,000 RETRIEVED (CMCSA Ex99.1). Other quarters INPUT. Leave blank if unused.</t>
         </is>
       </c>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="26" t="n">
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="25" t="n"/>
+      <c r="M14" s="24" t="n">
         <v>-65000</v>
       </c>
-      <c r="N14" s="27" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="27" t="n"/>
+      <c r="N14" s="25" t="n"/>
+      <c r="O14" s="25" t="n"/>
+      <c r="P14" s="25" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -3242,20 +2888,20 @@
           <t>Q1 2026 28,719,000 = 28,654k EOP − (−65k). Other quarters INPUT.</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="27" t="n"/>
-      <c r="J15" s="27" t="n"/>
-      <c r="K15" s="27" t="n"/>
-      <c r="L15" s="27" t="n"/>
-      <c r="M15" s="29" t="n">
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="25" t="n"/>
+      <c r="M15" s="27" t="n">
         <v>28719000</v>
       </c>
-      <c r="N15" s="27" t="n"/>
-      <c r="O15" s="27" t="n"/>
-      <c r="P15" s="27" t="n"/>
+      <c r="N15" s="25" t="n"/>
+      <c r="O15" s="25" t="n"/>
+      <c r="P15" s="25" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -3278,51 +2924,51 @@
           <t>Only when T9 and T10 are filled.</t>
         </is>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="28">
         <f>IF(OR(E14="",E15="",E15=0),"",ABS(E14)/E15)</f>
         <v/>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="28">
         <f>IF(OR(F14="",F15="",F15=0),"",ABS(F14)/F15)</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="28">
         <f>IF(OR(G14="",G15="",G15=0),"",ABS(G14)/G15)</f>
         <v/>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="28">
         <f>IF(OR(H14="",H15="",H15=0),"",ABS(H14)/H15)</f>
         <v/>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="28">
         <f>IF(OR(I14="",I15="",I15=0),"",ABS(I14)/I15)</f>
         <v/>
       </c>
-      <c r="J16" s="30">
+      <c r="J16" s="28">
         <f>IF(OR(J14="",J15="",J15=0),"",ABS(J14)/J15)</f>
         <v/>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="28">
         <f>IF(OR(K14="",K15="",K15=0),"",ABS(K14)/K15)</f>
         <v/>
       </c>
-      <c r="L16" s="30">
+      <c r="L16" s="28">
         <f>IF(OR(L14="",L15="",L15=0),"",ABS(L14)/L15)</f>
         <v/>
       </c>
-      <c r="M16" s="30">
+      <c r="M16" s="28">
         <f>IF(OR(M14="",M15="",M15=0),"",ABS(M14)/M15)</f>
         <v/>
       </c>
-      <c r="N16" s="30">
+      <c r="N16" s="28">
         <f>IF(OR(N14="",N15="",N15=0),"",ABS(N14)/N15)</f>
         <v/>
       </c>
-      <c r="O16" s="30">
+      <c r="O16" s="28">
         <f>IF(OR(O14="",O15="",O15=0),"",ABS(O14)/O15)</f>
         <v/>
       </c>
-      <c r="P16" s="30">
+      <c r="P16" s="28">
         <f>IF(OR(P14="",P15="",P15=0),"",ABS(P14)/P15)</f>
         <v/>
       </c>
@@ -3348,51 +2994,51 @@
           <t>Net-loss rate, not gross churn. Gross churn is unused because it is not disclosed.</t>
         </is>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="28">
         <f>IF(OR(E11="",E6="",E6=0),"",ABS(E11)/E6)</f>
         <v/>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="28">
         <f>IF(OR(F11="",F6="",F6=0),"",ABS(F11)/F6)</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="28">
         <f>IF(OR(G11="",G6="",G6=0),"",ABS(G11)/G6)</f>
         <v/>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="28">
         <f>IF(OR(H11="",H6="",H6=0),"",ABS(H11)/H6)</f>
         <v/>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="28">
         <f>IF(OR(I11="",I6="",I6=0),"",ABS(I11)/I6)</f>
         <v/>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="28">
         <f>IF(OR(J11="",J6="",J6=0),"",ABS(J11)/J6)</f>
         <v/>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="28">
         <f>IF(OR(K11="",K6="",K6=0),"",ABS(K11)/K6)</f>
         <v/>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="28">
         <f>IF(OR(L11="",L6="",L6=0),"",ABS(L11)/L6)</f>
         <v/>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="28">
         <f>IF(OR(M11="",M6="",M6=0),"",ABS(M11)/M6)</f>
         <v/>
       </c>
-      <c r="N17" s="30">
+      <c r="N17" s="28">
         <f>IF(OR(N11="",N6="",N6=0),"",ABS(N11)/N6)</f>
         <v/>
       </c>
-      <c r="O17" s="30">
+      <c r="O17" s="28">
         <f>IF(OR(O11="",O6="",O6=0),"",ABS(O11)/O6)</f>
         <v/>
       </c>
-      <c r="P17" s="30">
+      <c r="P17" s="28">
         <f>IF(OR(P11="",P6="",P6=0),"",ABS(P11)/P6)</f>
         <v/>
       </c>
@@ -3418,51 +3064,51 @@
           <t>Q1 playbook commit 1.8× (round down from 1.87×).</t>
         </is>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="29">
         <f>IF(OR(E16="",E17="",E16=0),"",E17/E16)</f>
         <v/>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="29">
         <f>IF(OR(F16="",F17="",F16=0),"",F17/F16)</f>
         <v/>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="29">
         <f>IF(OR(G16="",G17="",G16=0),"",G17/G16)</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="29">
         <f>IF(OR(H16="",H17="",H16=0),"",H17/H16)</f>
         <v/>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="29">
         <f>IF(OR(I16="",I17="",I16=0),"",I17/I16)</f>
         <v/>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="29">
         <f>IF(OR(J16="",J17="",J16=0),"",J17/J16)</f>
         <v/>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="29">
         <f>IF(OR(K16="",K17="",K16=0),"",K17/K16)</f>
         <v/>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="29">
         <f>IF(OR(L16="",L17="",L16=0),"",L17/L16)</f>
         <v/>
       </c>
-      <c r="M18" s="31">
+      <c r="M18" s="29">
         <f>IF(OR(M16="",M17="",M16=0),"",M17/M16)</f>
         <v/>
       </c>
-      <c r="N18" s="31">
+      <c r="N18" s="29">
         <f>IF(OR(N16="",N17="",N16=0),"",N17/N16)</f>
         <v/>
       </c>
-      <c r="O18" s="31">
+      <c r="O18" s="29">
         <f>IF(OR(O16="",O17="",O16=0),"",O17/O16)</f>
         <v/>
       </c>
-      <c r="P18" s="31">
+      <c r="P18" s="29">
         <f>IF(OR(P16="",P17="",P16=0),"",P17/P16)</f>
         <v/>
       </c>
@@ -3558,51 +3204,51 @@
           <t>Q1 identity ≈ 54.4k; playbook commits 54k (Parameters P18). Cite six-recommendation-areas.md.</t>
         </is>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="26">
         <f>IF(OR(E11="",E19=""),"",ABS(E11)-E19)</f>
         <v/>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="26">
         <f>IF(OR(F11="",F19=""),"",ABS(F11)-F19)</f>
         <v/>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="26">
         <f>IF(OR(G11="",G19=""),"",ABS(G11)-G19)</f>
         <v/>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="26">
         <f>IF(OR(H11="",H19=""),"",ABS(H11)-H19)</f>
         <v/>
       </c>
-      <c r="I20" s="28">
+      <c r="I20" s="26">
         <f>IF(OR(I11="",I19=""),"",ABS(I11)-I19)</f>
         <v/>
       </c>
-      <c r="J20" s="28">
+      <c r="J20" s="26">
         <f>IF(OR(J11="",J19=""),"",ABS(J11)-J19)</f>
         <v/>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="26">
         <f>IF(OR(K11="",K19=""),"",ABS(K11)-K19)</f>
         <v/>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="26">
         <f>IF(OR(L11="",L19=""),"",ABS(L11)-L19)</f>
         <v/>
       </c>
-      <c r="M20" s="28">
+      <c r="M20" s="26">
         <f>IF(OR(M11="",M19=""),"",ABS(M11)-M19)</f>
         <v/>
       </c>
-      <c r="N20" s="28">
+      <c r="N20" s="26">
         <f>IF(OR(N11="",N19=""),"",ABS(N11)-N19)</f>
         <v/>
       </c>
-      <c r="O20" s="28">
+      <c r="O20" s="26">
         <f>IF(OR(O11="",O19=""),"",ABS(O11)-O19)</f>
         <v/>
       </c>
-      <c r="P20" s="28">
+      <c r="P20" s="26">
         <f>IF(OR(P11="",P19=""),"",ABS(P11)-P19)</f>
         <v/>
       </c>
@@ -3868,7 +3514,7 @@
         </is>
       </c>
       <c r="B32" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$6:$P$6,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$6:$P$6,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$6:$P$6,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3879,7 +3525,7 @@
         </is>
       </c>
       <c r="B33" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$7:$P$7,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$7:$P$7,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$7:$P$7,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3890,7 +3536,7 @@
         </is>
       </c>
       <c r="B34" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$8:$P$8,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$8:$P$8,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$8:$P$8,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3901,7 +3547,7 @@
         </is>
       </c>
       <c r="B35" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$9:$P$9,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$9:$P$9,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$9:$P$9,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3912,7 +3558,7 @@
         </is>
       </c>
       <c r="B36" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$10:$P$10,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$10:$P$10,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$10:$P$10,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3923,7 +3569,7 @@
         </is>
       </c>
       <c r="B37" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$11:$P$11,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$11:$P$11,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$11:$P$11,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3934,7 +3580,7 @@
         </is>
       </c>
       <c r="B38" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$12:$P$12,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$12:$P$12,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$12:$P$12,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3945,7 +3591,7 @@
         </is>
       </c>
       <c r="B39" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$13:$P$13,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$13:$P$13,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$13:$P$13,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3956,7 +3602,7 @@
         </is>
       </c>
       <c r="B40" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$14:$P$14,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$14:$P$14,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$14:$P$14,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3967,7 +3613,7 @@
         </is>
       </c>
       <c r="B41" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$15:$P$15,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$15:$P$15,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$15:$P$15,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3977,8 +3623,8 @@
           <t>CMCSA rate</t>
         </is>
       </c>
-      <c r="B42" s="30">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$16:$P$16,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+      <c r="B42" s="28">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$16:$P$16,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$16:$P$16,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3988,8 +3634,8 @@
           <t>CHTR rate</t>
         </is>
       </c>
-      <c r="B43" s="30">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$17:$P$17,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+      <c r="B43" s="28">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$17:$P$17,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$17:$P$17,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -3999,8 +3645,8 @@
           <t>Rate ratio</t>
         </is>
       </c>
-      <c r="B44" s="31">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$18:$P$18,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+      <c r="B44" s="29">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$18:$P$18,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$18:$P$18,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -4011,7 +3657,7 @@
         </is>
       </c>
       <c r="B45" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$19:$P$19,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$19:$P$19,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$19:$P$19,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -4022,7 +3668,7 @@
         </is>
       </c>
       <c r="B46" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$20:$P$20,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$20:$P$20,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$20:$P$20,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -4033,7 +3679,7 @@
         </is>
       </c>
       <c r="B47" s="14">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$21:$P$21,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$21:$P$21,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$21:$P$21,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -4044,14 +3690,14 @@
         </is>
       </c>
       <c r="B48" s="12">
-        <f>IFERROR(INDEX('Net-loss tracker'!$E$22:$P$22,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Net-loss tracker'!$E$22:$P$22,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0)))=1,"",INDEX('Net-loss tracker'!$E$22:$P$22,MATCH(Param_Quarter,'Net-loss tracker'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Engine rows 32–48 feed the Dashboard. Q3–Q4 2026 begin/print stay blank until Ex99.1 or internals exist.</t>
+          <t>Engine rows 32–48 feed the Dashboard KPIs. Rows 53–54 are the line-chart feed (NA() = gap, not a zero). Q3–Q4 2026 begin/print stay blank until Ex99.1 or internals exist.</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -4062,10 +3708,195 @@
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="3" t="n"/>
     </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>DASHBOARD LINE-CHART FEED (NA gaps — do not edit)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>CHTR plot</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>CHTR res. Internet</t>
+        </is>
+      </c>
+      <c r="E53" s="14">
+        <f>IF(E11="",NA(),E11)</f>
+        <v/>
+      </c>
+      <c r="F53" s="14">
+        <f>IF(F11="",NA(),F11)</f>
+        <v/>
+      </c>
+      <c r="G53" s="14">
+        <f>IF(G11="",NA(),G11)</f>
+        <v/>
+      </c>
+      <c r="H53" s="14">
+        <f>IF(H11="",NA(),H11)</f>
+        <v/>
+      </c>
+      <c r="I53" s="14">
+        <f>IF(I11="",NA(),I11)</f>
+        <v/>
+      </c>
+      <c r="J53" s="14">
+        <f>IF(J11="",NA(),J11)</f>
+        <v/>
+      </c>
+      <c r="K53" s="14">
+        <f>IF(K11="",NA(),K11)</f>
+        <v/>
+      </c>
+      <c r="L53" s="14">
+        <f>IF(L11="",NA(),L11)</f>
+        <v/>
+      </c>
+      <c r="M53" s="14">
+        <f>IF(M11="",NA(),M11)</f>
+        <v/>
+      </c>
+      <c r="N53" s="14">
+        <f>IF(N11="",NA(),N11)</f>
+        <v/>
+      </c>
+      <c r="O53" s="14">
+        <f>IF(O11="",NA(),O11)</f>
+        <v/>
+      </c>
+      <c r="P53" s="14">
+        <f>IF(P11="",NA(),P11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>CMCSA plot</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>CMCSA resid. BB</t>
+        </is>
+      </c>
+      <c r="E54" s="14">
+        <f>IF(E14="",NA(),E14)</f>
+        <v/>
+      </c>
+      <c r="F54" s="14">
+        <f>IF(F14="",NA(),F14)</f>
+        <v/>
+      </c>
+      <c r="G54" s="14">
+        <f>IF(G14="",NA(),G14)</f>
+        <v/>
+      </c>
+      <c r="H54" s="14">
+        <f>IF(H14="",NA(),H14)</f>
+        <v/>
+      </c>
+      <c r="I54" s="14">
+        <f>IF(I14="",NA(),I14)</f>
+        <v/>
+      </c>
+      <c r="J54" s="14">
+        <f>IF(J14="",NA(),J14)</f>
+        <v/>
+      </c>
+      <c r="K54" s="14">
+        <f>IF(K14="",NA(),K14)</f>
+        <v/>
+      </c>
+      <c r="L54" s="14">
+        <f>IF(L14="",NA(),L14)</f>
+        <v/>
+      </c>
+      <c r="M54" s="14">
+        <f>IF(M14="",NA(),M14)</f>
+        <v/>
+      </c>
+      <c r="N54" s="14">
+        <f>IF(N14="",NA(),N14)</f>
+        <v/>
+      </c>
+      <c r="O54" s="14">
+        <f>IF(O14="",NA(),O14)</f>
+        <v/>
+      </c>
+      <c r="P54" s="14">
+        <f>IF(P14="",NA(),P14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Overlap flag (both T6 and T9 filled)</t>
+        </is>
+      </c>
+      <c r="E56" s="12">
+        <f>IF(AND(E11&lt;&gt;"",E14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="F56" s="12">
+        <f>IF(AND(F11&lt;&gt;"",F14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="G56" s="12">
+        <f>IF(AND(G11&lt;&gt;"",G14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="H56" s="12">
+        <f>IF(AND(H11&lt;&gt;"",H14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="I56" s="12">
+        <f>IF(AND(I11&lt;&gt;"",I14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="J56" s="12">
+        <f>IF(AND(J11&lt;&gt;"",J14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="K56" s="12">
+        <f>IF(AND(K11&lt;&gt;"",K14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="L56" s="12">
+        <f>IF(AND(L11&lt;&gt;"",L14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="M56" s="12">
+        <f>IF(AND(M11&lt;&gt;"",M14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="N56" s="12">
+        <f>IF(AND(N11&lt;&gt;"",N14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="O56" s="12">
+        <f>IF(AND(O11&lt;&gt;"",O14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+      <c r="P56" s="12">
+        <f>IF(AND(P11&lt;&gt;"",P14&lt;&gt;""),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A5:P5"/>
-  <mergeCells count="10">
+  <autoFilter ref="A5:P22"/>
+  <mergeCells count="11">
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A27:L27"/>
     <mergeCell ref="A50:H50"/>
@@ -4075,6 +3906,7 @@
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4135,34 +3967,34 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>PPTX cause-cohorts: FWA-covered · fiber-overbuilt · satellite-only · housing/move-out · non-pay · residual. GAP R1–R4 maps onto the same rows (satellite is pptx-only). Enter COUNTS of sampled disconnects (yellow). Residual is a formula. Empty cells are on purpose — the playbook will not fire from a guess.</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="16" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="17" t="n"/>
+          <t>Paste COUNTS of sampled disconnects in yellow (start cell E6). Residual is a formula. Dashboard fires GAP R1–R4 from A1–A6 only. Residual cannot win rank or fire a play. Empty cells are on purpose — the playbook will not fire from a guess.</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n"/>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="n"/>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="21" t="n"/>
-      <c r="I3" s="21" t="n"/>
-      <c r="J3" s="21" t="n"/>
-      <c r="K3" s="21" t="n"/>
-      <c r="L3" s="22" t="n"/>
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="23" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
@@ -4263,21 +4095,21 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>S1 / R2</t>
-        </is>
-      </c>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="27" t="n"/>
-      <c r="J6" s="27" t="n"/>
-      <c r="K6" s="27" t="n"/>
-      <c r="L6" s="27" t="n"/>
-      <c r="M6" s="27" t="n"/>
-      <c r="N6" s="27" t="n"/>
-      <c r="O6" s="27" t="n"/>
-      <c r="P6" s="27" t="n"/>
+          <t>GAP R2</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="25" t="n"/>
+      <c r="M6" s="25" t="n"/>
+      <c r="N6" s="25" t="n"/>
+      <c r="O6" s="25" t="n"/>
+      <c r="P6" s="25" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -4296,21 +4128,21 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>S2 / R3</t>
-        </is>
-      </c>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
+          <t>GAP R3</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="25" t="n"/>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="25" t="n"/>
+      <c r="L7" s="25" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="25" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -4329,21 +4161,21 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>S3 / W2</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="27" t="n"/>
-      <c r="O8" s="27" t="n"/>
-      <c r="P8" s="27" t="n"/>
+          <t>W2 overlay</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="L8" s="25" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="25" t="n"/>
+      <c r="O8" s="25" t="n"/>
+      <c r="P8" s="25" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -4362,21 +4194,21 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>S4 / R1</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="27" t="n"/>
-      <c r="J9" s="27" t="n"/>
-      <c r="K9" s="27" t="n"/>
-      <c r="L9" s="27" t="n"/>
-      <c r="M9" s="27" t="n"/>
-      <c r="N9" s="27" t="n"/>
-      <c r="O9" s="27" t="n"/>
-      <c r="P9" s="27" t="n"/>
+          <t>GAP R1</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="25" t="n"/>
+      <c r="L9" s="25" t="n"/>
+      <c r="M9" s="25" t="n"/>
+      <c r="N9" s="25" t="n"/>
+      <c r="O9" s="25" t="n"/>
+      <c r="P9" s="25" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -4395,21 +4227,21 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>S5 / R4</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="27" t="n"/>
-      <c r="M10" s="27" t="n"/>
-      <c r="N10" s="27" t="n"/>
-      <c r="O10" s="27" t="n"/>
-      <c r="P10" s="27" t="n"/>
+          <t>GAP R4</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="25" t="n"/>
+      <c r="L10" s="25" t="n"/>
+      <c r="M10" s="25" t="n"/>
+      <c r="N10" s="25" t="n"/>
+      <c r="O10" s="25" t="n"/>
+      <c r="P10" s="25" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -4428,21 +4260,21 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Residual</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-      <c r="O11" s="27" t="n"/>
-      <c r="P11" s="27" t="n"/>
+          <t>FLAG only</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="25" t="n"/>
+      <c r="L11" s="25" t="n"/>
+      <c r="M11" s="25" t="n"/>
+      <c r="N11" s="25" t="n"/>
+      <c r="O11" s="25" t="n"/>
+      <c r="P11" s="25" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -4465,51 +4297,51 @@
           <t>Largest residual is a data-quality flag</t>
         </is>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="26">
         <f>IF(E14="","",E14-SUM(E6:E11))</f>
         <v/>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="26">
         <f>IF(F14="","",F14-SUM(F6:F11))</f>
         <v/>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="26">
         <f>IF(G14="","",G14-SUM(G6:G11))</f>
         <v/>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="26">
         <f>IF(H14="","",H14-SUM(H6:H11))</f>
         <v/>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="26">
         <f>IF(I14="","",I14-SUM(I6:I11))</f>
         <v/>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="26">
         <f>IF(J14="","",J14-SUM(J6:J11))</f>
         <v/>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="26">
         <f>IF(K14="","",K14-SUM(K6:K11))</f>
         <v/>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="26">
         <f>IF(L14="","",L14-SUM(L6:L11))</f>
         <v/>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="26">
         <f>IF(M14="","",M14-SUM(M6:M11))</f>
         <v/>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="26">
         <f>IF(N14="","",N14-SUM(N6:N11))</f>
         <v/>
       </c>
-      <c r="O12" s="28">
+      <c r="O12" s="26">
         <f>IF(O14="","",O14-SUM(O6:O11))</f>
         <v/>
       </c>
-      <c r="P12" s="28">
+      <c r="P12" s="26">
         <f>IF(P14="","",P14-SUM(P6:P11))</f>
         <v/>
       </c>
@@ -4592,7 +4424,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Tracker disconnects (T3) — or |print| placeholder</t>
+          <t>Tracker disconnects (T3) — Counts base; blank until T3 is pasted</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4602,55 +4434,55 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>If T3 blank and mode is Percent, uses |T6| and labels PLACEHOLDER</t>
+          <t>Percent / |print| allocation removed — cannot fire a scaled play</t>
         </is>
       </c>
       <c r="E14" s="14">
-        <f>IF('Net-loss tracker'!E8&lt;&gt;"",'Net-loss tracker'!E8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!E11&lt;&gt;""),ABS('Net-loss tracker'!E11),""))</f>
+        <f>IF('Net-loss tracker'!E8&lt;&gt;"",'Net-loss tracker'!E8,"")</f>
         <v/>
       </c>
       <c r="F14" s="14">
-        <f>IF('Net-loss tracker'!F8&lt;&gt;"",'Net-loss tracker'!F8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!F11&lt;&gt;""),ABS('Net-loss tracker'!F11),""))</f>
+        <f>IF('Net-loss tracker'!F8&lt;&gt;"",'Net-loss tracker'!F8,"")</f>
         <v/>
       </c>
       <c r="G14" s="14">
-        <f>IF('Net-loss tracker'!G8&lt;&gt;"",'Net-loss tracker'!G8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!G11&lt;&gt;""),ABS('Net-loss tracker'!G11),""))</f>
+        <f>IF('Net-loss tracker'!G8&lt;&gt;"",'Net-loss tracker'!G8,"")</f>
         <v/>
       </c>
       <c r="H14" s="14">
-        <f>IF('Net-loss tracker'!H8&lt;&gt;"",'Net-loss tracker'!H8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!H11&lt;&gt;""),ABS('Net-loss tracker'!H11),""))</f>
+        <f>IF('Net-loss tracker'!H8&lt;&gt;"",'Net-loss tracker'!H8,"")</f>
         <v/>
       </c>
       <c r="I14" s="14">
-        <f>IF('Net-loss tracker'!I8&lt;&gt;"",'Net-loss tracker'!I8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!I11&lt;&gt;""),ABS('Net-loss tracker'!I11),""))</f>
+        <f>IF('Net-loss tracker'!I8&lt;&gt;"",'Net-loss tracker'!I8,"")</f>
         <v/>
       </c>
       <c r="J14" s="14">
-        <f>IF('Net-loss tracker'!J8&lt;&gt;"",'Net-loss tracker'!J8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!J11&lt;&gt;""),ABS('Net-loss tracker'!J11),""))</f>
+        <f>IF('Net-loss tracker'!J8&lt;&gt;"",'Net-loss tracker'!J8,"")</f>
         <v/>
       </c>
       <c r="K14" s="14">
-        <f>IF('Net-loss tracker'!K8&lt;&gt;"",'Net-loss tracker'!K8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!K11&lt;&gt;""),ABS('Net-loss tracker'!K11),""))</f>
+        <f>IF('Net-loss tracker'!K8&lt;&gt;"",'Net-loss tracker'!K8,"")</f>
         <v/>
       </c>
       <c r="L14" s="14">
-        <f>IF('Net-loss tracker'!L8&lt;&gt;"",'Net-loss tracker'!L8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!L11&lt;&gt;""),ABS('Net-loss tracker'!L11),""))</f>
+        <f>IF('Net-loss tracker'!L8&lt;&gt;"",'Net-loss tracker'!L8,"")</f>
         <v/>
       </c>
       <c r="M14" s="14">
-        <f>IF('Net-loss tracker'!M8&lt;&gt;"",'Net-loss tracker'!M8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!M11&lt;&gt;""),ABS('Net-loss tracker'!M11),""))</f>
+        <f>IF('Net-loss tracker'!M8&lt;&gt;"",'Net-loss tracker'!M8,"")</f>
         <v/>
       </c>
       <c r="N14" s="14">
-        <f>IF('Net-loss tracker'!N8&lt;&gt;"",'Net-loss tracker'!N8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!N11&lt;&gt;""),ABS('Net-loss tracker'!N11),""))</f>
+        <f>IF('Net-loss tracker'!N8&lt;&gt;"",'Net-loss tracker'!N8,"")</f>
         <v/>
       </c>
       <c r="O14" s="14">
-        <f>IF('Net-loss tracker'!O8&lt;&gt;"",'Net-loss tracker'!O8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!O11&lt;&gt;""),ABS('Net-loss tracker'!O11),""))</f>
+        <f>IF('Net-loss tracker'!O8&lt;&gt;"",'Net-loss tracker'!O8,"")</f>
         <v/>
       </c>
       <c r="P14" s="14">
-        <f>IF('Net-loss tracker'!P8&lt;&gt;"",'Net-loss tracker'!P8,IF(AND(Parameters!$C$19="Percent",'Net-loss tracker'!P11&lt;&gt;""),ABS('Net-loss tracker'!P11),""))</f>
+        <f>IF('Net-loss tracker'!P8&lt;&gt;"",'Net-loss tracker'!P8,"")</f>
         <v/>
       </c>
     </row>
@@ -4672,55 +4504,55 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Empty until a reason or residual exists</t>
+          <t>HOLD if residual is largest or ≥2% of T3</t>
         </is>
       </c>
       <c r="E15" s="12">
-        <f>IF(AND(COUNT(E6:E11)=0,E14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!E8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(E12))&gt;0.02*MAX(1,N(E14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(E6:E11)=0,E14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!E8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(E12))&gt;0.02*MAX(1,N(E14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>IF(AND(COUNT(F6:F11)=0,F14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!F8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(F12))&gt;0.02*MAX(1,N(F14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(F6:F11)=0,F14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!F8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(F12))&gt;0.02*MAX(1,N(F14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="G15" s="12">
-        <f>IF(AND(COUNT(G6:G11)=0,G14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!G8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(G12))&gt;0.02*MAX(1,N(G14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(G6:G11)=0,G14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!G8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(G12))&gt;0.02*MAX(1,N(G14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="H15" s="12">
-        <f>IF(AND(COUNT(H6:H11)=0,H14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!H8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(H12))&gt;0.02*MAX(1,N(H14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(H6:H11)=0,H14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!H8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(H12))&gt;0.02*MAX(1,N(H14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="I15" s="12">
-        <f>IF(AND(COUNT(I6:I11)=0,I14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!I8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(I12))&gt;0.02*MAX(1,N(I14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(I6:I11)=0,I14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!I8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(I12))&gt;0.02*MAX(1,N(I14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="J15" s="12">
-        <f>IF(AND(COUNT(J6:J11)=0,J14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!J8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(J12))&gt;0.02*MAX(1,N(J14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(J6:J11)=0,J14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!J8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(J12))&gt;0.02*MAX(1,N(J14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="K15" s="12">
-        <f>IF(AND(COUNT(K6:K11)=0,K14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!K8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(K12))&gt;0.02*MAX(1,N(K14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(K6:K11)=0,K14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!K8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(K12))&gt;0.02*MAX(1,N(K14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="L15" s="12">
-        <f>IF(AND(COUNT(L6:L11)=0,L14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!L8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(L12))&gt;0.02*MAX(1,N(L14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(L6:L11)=0,L14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!L8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(L12))&gt;0.02*MAX(1,N(L14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="M15" s="12">
-        <f>IF(AND(COUNT(M6:M11)=0,M14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!M8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(M12))&gt;0.02*MAX(1,N(M14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(M6:M11)=0,M14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!M8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(M12))&gt;0.02*MAX(1,N(M14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="N15" s="12">
-        <f>IF(AND(COUNT(N6:N11)=0,N14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!N8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(N12))&gt;0.02*MAX(1,N(N14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(N6:N11)=0,N14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!N8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(N12))&gt;0.02*MAX(1,N(N14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="O15" s="12">
-        <f>IF(AND(COUNT(O6:O11)=0,O14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!O8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(O12))&gt;0.02*MAX(1,N(O14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(O6:O11)=0,O14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!O8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(O12))&gt;0.02*MAX(1,N(O14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
       <c r="P15" s="12">
-        <f>IF(AND(COUNT(P6:P11)=0,P14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!P8="","PLACEHOLDER — allocating |print|, not a churn mix",IF(ABS(N(P12))&gt;0.02*MAX(1,N(P14)),"FLAG — residual is material","OK — reasons reconcile")))</f>
+        <f>IF(AND(COUNT(P6:P11)=0,P14=""),"EMPTY — do not fire a play",IF('Net-loss tracker'!P8="","HOLD — T3 disconnects required (Counts). |print| is not a mix",IF(ABS(N(P12))&gt;0.02*MAX(1,N(P14)),"FLAG — residual is material — HOLD","OK — reasons reconcile")))</f>
         <v/>
       </c>
     </row>
@@ -5947,7 +5779,7 @@
         <v/>
       </c>
       <c r="C40" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$6:$P$6,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$6:$P$6,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$6:$P$6,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D40" s="15">
@@ -5963,7 +5795,7 @@
         <v/>
       </c>
       <c r="G40" s="12">
-        <f>IF(SUM($F$40:$F$46)=0,"",RANK(F40,$F$40:$F$46,0))</f>
+        <f>IF(SUM($F$40:$F$45)=0,"",RANK(F40,$F$40:$F$45,0))</f>
         <v/>
       </c>
       <c r="H40" s="12">
@@ -5971,11 +5803,11 @@
         <v/>
       </c>
       <c r="I40" s="14">
-        <f>IF(G40=1,0,IF(C40="",NA(),C40))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G40=1,0,IF(C40="",NA(),C40)))</f>
         <v/>
       </c>
       <c r="J40" s="14">
-        <f>IF(G40=1,IF(C40="",NA(),C40),0)</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G40=1,IF(C40="",NA(),C40),0))</f>
         <v/>
       </c>
     </row>
@@ -5988,7 +5820,7 @@
         <v/>
       </c>
       <c r="C41" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$7:$P$7,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$7:$P$7,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$7:$P$7,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D41" s="15">
@@ -6004,7 +5836,7 @@
         <v/>
       </c>
       <c r="G41" s="12">
-        <f>IF(SUM($F$40:$F$46)=0,"",RANK(F41,$F$40:$F$46,0))</f>
+        <f>IF(SUM($F$40:$F$45)=0,"",RANK(F41,$F$40:$F$45,0))</f>
         <v/>
       </c>
       <c r="H41" s="12">
@@ -6012,11 +5844,11 @@
         <v/>
       </c>
       <c r="I41" s="14">
-        <f>IF(G41=1,0,IF(C41="",NA(),C41))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G41=1,0,IF(C41="",NA(),C41)))</f>
         <v/>
       </c>
       <c r="J41" s="14">
-        <f>IF(G41=1,IF(C41="",NA(),C41),0)</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G41=1,IF(C41="",NA(),C41),0))</f>
         <v/>
       </c>
     </row>
@@ -6029,7 +5861,7 @@
         <v/>
       </c>
       <c r="C42" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$8:$P$8,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$8:$P$8,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$8:$P$8,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D42" s="15">
@@ -6045,7 +5877,7 @@
         <v/>
       </c>
       <c r="G42" s="12">
-        <f>IF(SUM($F$40:$F$46)=0,"",RANK(F42,$F$40:$F$46,0))</f>
+        <f>IF(SUM($F$40:$F$45)=0,"",RANK(F42,$F$40:$F$45,0))</f>
         <v/>
       </c>
       <c r="H42" s="12">
@@ -6053,11 +5885,11 @@
         <v/>
       </c>
       <c r="I42" s="14">
-        <f>IF(G42=1,0,IF(C42="",NA(),C42))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G42=1,0,IF(C42="",NA(),C42)))</f>
         <v/>
       </c>
       <c r="J42" s="14">
-        <f>IF(G42=1,IF(C42="",NA(),C42),0)</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G42=1,IF(C42="",NA(),C42),0))</f>
         <v/>
       </c>
     </row>
@@ -6070,7 +5902,7 @@
         <v/>
       </c>
       <c r="C43" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$9:$P$9,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$9:$P$9,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$9:$P$9,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D43" s="15">
@@ -6086,7 +5918,7 @@
         <v/>
       </c>
       <c r="G43" s="12">
-        <f>IF(SUM($F$40:$F$46)=0,"",RANK(F43,$F$40:$F$46,0))</f>
+        <f>IF(SUM($F$40:$F$45)=0,"",RANK(F43,$F$40:$F$45,0))</f>
         <v/>
       </c>
       <c r="H43" s="12">
@@ -6094,11 +5926,11 @@
         <v/>
       </c>
       <c r="I43" s="14">
-        <f>IF(G43=1,0,IF(C43="",NA(),C43))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G43=1,0,IF(C43="",NA(),C43)))</f>
         <v/>
       </c>
       <c r="J43" s="14">
-        <f>IF(G43=1,IF(C43="",NA(),C43),0)</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G43=1,IF(C43="",NA(),C43),0))</f>
         <v/>
       </c>
     </row>
@@ -6111,7 +5943,7 @@
         <v/>
       </c>
       <c r="C44" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$10:$P$10,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$10:$P$10,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$10:$P$10,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D44" s="15">
@@ -6127,7 +5959,7 @@
         <v/>
       </c>
       <c r="G44" s="12">
-        <f>IF(SUM($F$40:$F$46)=0,"",RANK(F44,$F$40:$F$46,0))</f>
+        <f>IF(SUM($F$40:$F$45)=0,"",RANK(F44,$F$40:$F$45,0))</f>
         <v/>
       </c>
       <c r="H44" s="12">
@@ -6135,11 +5967,11 @@
         <v/>
       </c>
       <c r="I44" s="14">
-        <f>IF(G44=1,0,IF(C44="",NA(),C44))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G44=1,0,IF(C44="",NA(),C44)))</f>
         <v/>
       </c>
       <c r="J44" s="14">
-        <f>IF(G44=1,IF(C44="",NA(),C44),0)</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G44=1,IF(C44="",NA(),C44),0))</f>
         <v/>
       </c>
     </row>
@@ -6152,7 +5984,7 @@
         <v/>
       </c>
       <c r="C45" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$11:$P$11,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$11:$P$11,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$11:$P$11,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D45" s="15">
@@ -6168,7 +6000,7 @@
         <v/>
       </c>
       <c r="G45" s="12">
-        <f>IF(SUM($F$40:$F$46)=0,"",RANK(F45,$F$40:$F$46,0))</f>
+        <f>IF(SUM($F$40:$F$45)=0,"",RANK(F45,$F$40:$F$45,0))</f>
         <v/>
       </c>
       <c r="H45" s="12">
@@ -6176,11 +6008,11 @@
         <v/>
       </c>
       <c r="I45" s="14">
-        <f>IF(G45=1,0,IF(C45="",NA(),C45))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G45=1,0,IF(C45="",NA(),C45)))</f>
         <v/>
       </c>
       <c r="J45" s="14">
-        <f>IF(G45=1,IF(C45="",NA(),C45),0)</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(G45=1,IF(C45="",NA(),C45),0))</f>
         <v/>
       </c>
     </row>
@@ -6193,7 +6025,7 @@
         <v/>
       </c>
       <c r="C46" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$12:$P$12,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$12:$P$12,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$12:$P$12,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D46" s="15">
@@ -6208,20 +6040,22 @@
         <f>IF(C46="",0,ABS(C46))</f>
         <v/>
       </c>
-      <c r="G46" s="12">
-        <f>IF(SUM($F$40:$F$46)=0,"",RANK(F46,$F$40:$F$46,0))</f>
-        <v/>
-      </c>
-      <c r="H46" s="12">
-        <f>IF(G46=1,"LARGEST","")</f>
-        <v/>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>FLAG only — cannot fire</t>
+        </is>
       </c>
       <c r="I46" s="14">
-        <f>IF(G46=1,0,IF(C46="",NA(),C46))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="J46" s="14">
-        <f>IF(G46=1,IF(C46="",NA(),C46),0)</f>
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -6233,11 +6067,11 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Disconnects / allocation base</t>
+          <t>Disconnects / allocation base (T3 only)</t>
         </is>
       </c>
       <c r="C47" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$14:$P$14,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$14:$P$14,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$14:$P$14,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -6249,15 +6083,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Largest reason share of base</t>
+          <t>Largest A1–A6 share of base (residual excluded)</t>
         </is>
       </c>
       <c r="C48" s="15">
-        <f>IF(COUNT(D40:D46)=0,"",MAX(D40:D46))</f>
+        <f>IF(COUNT(D40:D45)=0,"",MAX(D40:D45))</f>
         <v/>
       </c>
       <c r="D48" s="12">
-        <f>IF(C48="","",INDEX(B40:B46,MATCH(C48,D40:D46,0)))</f>
+        <f>IF(C48="","",INDEX(B40:B45,MATCH(C48,D40:D45,0)))</f>
         <v/>
       </c>
     </row>
@@ -6269,11 +6103,11 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Any reason count filled this quarter?</t>
+          <t>A1–A6 counts in selected quarter AND T3 filled?</t>
         </is>
       </c>
       <c r="C49" s="12">
-        <f>IF(COUNT(C40:C45)=0,"No","Yes")</f>
+        <f>IFERROR(IF(OR(COUNT(INDEX($E$6:$P$11,0,MATCH(Param_Quarter,$E$5:$P$5,0)))=0,COUNTBLANK(INDEX($E$14:$P$14,MATCH(Param_Quarter,$E$5:$P$5,0)))=1),"No","Yes"),"No")</f>
         <v/>
       </c>
     </row>
@@ -6285,230 +6119,237 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2nd-largest share (mixed test)</t>
+          <t>2nd-largest A1–A6 share (mixed test)</t>
         </is>
       </c>
       <c r="C50" s="15">
-        <f>IF(COUNT(D40:D46)&lt;2,"",LARGE(D40:D46,2))</f>
+        <f>IF(COUNT(D40:D45)&lt;2,"",LARGE(D40:D45,2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Residual gate</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>HOLD if residual is largest vs A1–A6 or ≥2% of T3</t>
+        </is>
+      </c>
+      <c r="C51" s="12">
+        <f>IF(OR(C49&lt;&gt;"Yes",C47=""),"",IF(OR(N(C46)&gt;=0.02*MAX(1,N(C47)),AND(COUNT(D40:D45)&gt;0,N(D46)&gt;=MAX(D40:D45))),"HOLD","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>SORTED FOR CHART (magnitude descending)</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="3" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Prior max</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Prior-quarter max A1–A6 share (two-quarter interlock)</t>
+        </is>
+      </c>
+      <c r="C52" s="15">
+        <f>IFERROR(IF(MATCH(Param_Quarter,$E$5:$P$5,0)=1,"",IF(COUNT(INDEX($E$19:$P$24,0,MATCH(Param_Quarter,$E$5:$P$5,0)-1))=0,"",MAX(INDEX($E$19:$P$24,0,MATCH(Param_Quarter,$E$5:$P$5,0)-1)))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>SORTED FOR CHART (A1–A6 only, magnitude descending)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>Rest (gray)</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Largest (accent)</t>
         </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B54" s="12">
-        <f>IF($C$49="No","",IFERROR(INDEX($B$40:$B$46,MATCH(1,$G$40:$G$46,0)),""))</f>
-        <v/>
-      </c>
-      <c r="C54" s="14">
-        <f>IF(B54="","",IFERROR(INDEX($C$40:$C$46,MATCH(1,$G$40:$G$46,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D54" s="15">
-        <f>IF(B54="","",IFERROR(INDEX($D$40:$D$46,MATCH(1,$G$40:$G$46,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E54" s="14">
-        <f>IF(OR(B54="",C54=""),NA(),IF(A54=1,0,C54))</f>
-        <v/>
-      </c>
-      <c r="F54" s="14">
-        <f>IF(OR(B54="",C54=""),NA(),IF(A54=1,C54,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B55" s="12">
-        <f>IF($C$49="No","",IFERROR(INDEX($B$40:$B$46,MATCH(2,$G$40:$G$46,0)),""))</f>
-        <v/>
-      </c>
-      <c r="C55" s="14">
-        <f>IF(B55="","",IFERROR(INDEX($C$40:$C$46,MATCH(2,$G$40:$G$46,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D55" s="15">
-        <f>IF(B55="","",IFERROR(INDEX($D$40:$D$46,MATCH(2,$G$40:$G$46,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E55" s="14">
-        <f>IF(OR(B55="",C55=""),NA(),IF(A55=1,0,C55))</f>
-        <v/>
-      </c>
-      <c r="F55" s="14">
-        <f>IF(OR(B55="",C55=""),NA(),IF(A55=1,C55,0))</f>
-        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B56" s="12">
-        <f>IF($C$49="No","",IFERROR(INDEX($B$40:$B$46,MATCH(3,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($B$40:$B$45,MATCH(1,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="C56" s="14">
-        <f>IF(B56="","",IFERROR(INDEX($C$40:$C$46,MATCH(3,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($C$40:$C$45,MATCH(1,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="D56" s="15">
-        <f>IF(B56="","",IFERROR(INDEX($D$40:$D$46,MATCH(3,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($D$40:$D$45,MATCH(1,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="E56" s="14">
-        <f>IF(OR(B56="",C56=""),NA(),IF(A56=1,0,C56))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A56=1,0,C56))</f>
         <v/>
       </c>
       <c r="F56" s="14">
-        <f>IF(OR(B56="",C56=""),NA(),IF(A56=1,C56,0))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A56=1,C56,0))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B57" s="12">
-        <f>IF($C$49="No","",IFERROR(INDEX($B$40:$B$46,MATCH(4,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($B$40:$B$45,MATCH(2,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="C57" s="14">
-        <f>IF(B57="","",IFERROR(INDEX($C$40:$C$46,MATCH(4,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($C$40:$C$45,MATCH(2,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="D57" s="15">
-        <f>IF(B57="","",IFERROR(INDEX($D$40:$D$46,MATCH(4,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($D$40:$D$45,MATCH(2,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="E57" s="14">
-        <f>IF(OR(B57="",C57=""),NA(),IF(A57=1,0,C57))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A57=1,0,C57))</f>
         <v/>
       </c>
       <c r="F57" s="14">
-        <f>IF(OR(B57="",C57=""),NA(),IF(A57=1,C57,0))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A57=1,C57,0))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B58" s="12">
-        <f>IF($C$49="No","",IFERROR(INDEX($B$40:$B$46,MATCH(5,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($B$40:$B$45,MATCH(3,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="C58" s="14">
-        <f>IF(B58="","",IFERROR(INDEX($C$40:$C$46,MATCH(5,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($C$40:$C$45,MATCH(3,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="D58" s="15">
-        <f>IF(B58="","",IFERROR(INDEX($D$40:$D$46,MATCH(5,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($D$40:$D$45,MATCH(3,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="E58" s="14">
-        <f>IF(OR(B58="",C58=""),NA(),IF(A58=1,0,C58))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A58=1,0,C58))</f>
         <v/>
       </c>
       <c r="F58" s="14">
-        <f>IF(OR(B58="",C58=""),NA(),IF(A58=1,C58,0))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A58=1,C58,0))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B59" s="12">
-        <f>IF($C$49="No","",IFERROR(INDEX($B$40:$B$46,MATCH(6,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($B$40:$B$45,MATCH(4,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="C59" s="14">
-        <f>IF(B59="","",IFERROR(INDEX($C$40:$C$46,MATCH(6,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($C$40:$C$45,MATCH(4,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="D59" s="15">
-        <f>IF(B59="","",IFERROR(INDEX($D$40:$D$46,MATCH(6,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($D$40:$D$45,MATCH(4,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="E59" s="14">
-        <f>IF(OR(B59="",C59=""),NA(),IF(A59=1,0,C59))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A59=1,0,C59))</f>
         <v/>
       </c>
       <c r="F59" s="14">
-        <f>IF(OR(B59="",C59=""),NA(),IF(A59=1,C59,0))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A59=1,C59,0))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B60" s="12">
-        <f>IF($C$49="No","",IFERROR(INDEX($B$40:$B$46,MATCH(7,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($B$40:$B$45,MATCH(5,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="C60" s="14">
-        <f>IF(B60="","",IFERROR(INDEX($C$40:$C$46,MATCH(7,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($C$40:$C$45,MATCH(5,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="D60" s="15">
-        <f>IF(B60="","",IFERROR(INDEX($D$40:$D$46,MATCH(7,$G$40:$G$46,0)),""))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($D$40:$D$45,MATCH(5,$G$40:$G$45,0)),NA()))</f>
         <v/>
       </c>
       <c r="E60" s="14">
-        <f>IF(OR(B60="",C60=""),NA(),IF(A60=1,0,C60))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A60=1,0,C60))</f>
         <v/>
       </c>
       <c r="F60" s="14">
-        <f>IF(OR(B60="",C60=""),NA(),IF(A60=1,C60,0))</f>
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A60=1,C60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B61" s="12">
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($B$40:$B$45,MATCH(6,$G$40:$G$45,0)),NA()))</f>
+        <v/>
+      </c>
+      <c r="C61" s="14">
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($C$40:$C$45,MATCH(6,$G$40:$G$45,0)),NA()))</f>
+        <v/>
+      </c>
+      <c r="D61" s="15">
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IFERROR(INDEX($D$40:$D$45,MATCH(6,$G$40:$G$45,0)),NA()))</f>
+        <v/>
+      </c>
+      <c r="E61" s="14">
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A61=1,0,C61))</f>
+        <v/>
+      </c>
+      <c r="F61" s="14">
+        <f>IF($C$49&lt;&gt;"Yes",NA(),IF(A61=1,C61,0))</f>
         <v/>
       </c>
     </row>
@@ -6643,18 +6484,18 @@
           <t>Disconnect counts in this class</t>
         </is>
       </c>
-      <c r="E66" s="27" t="n"/>
-      <c r="F66" s="27" t="n"/>
-      <c r="G66" s="27" t="n"/>
-      <c r="H66" s="27" t="n"/>
-      <c r="I66" s="27" t="n"/>
-      <c r="J66" s="27" t="n"/>
-      <c r="K66" s="27" t="n"/>
-      <c r="L66" s="27" t="n"/>
-      <c r="M66" s="27" t="n"/>
-      <c r="N66" s="27" t="n"/>
-      <c r="O66" s="27" t="n"/>
-      <c r="P66" s="27" t="n"/>
+      <c r="E66" s="25" t="n"/>
+      <c r="F66" s="25" t="n"/>
+      <c r="G66" s="25" t="n"/>
+      <c r="H66" s="25" t="n"/>
+      <c r="I66" s="25" t="n"/>
+      <c r="J66" s="25" t="n"/>
+      <c r="K66" s="25" t="n"/>
+      <c r="L66" s="25" t="n"/>
+      <c r="M66" s="25" t="n"/>
+      <c r="N66" s="25" t="n"/>
+      <c r="O66" s="25" t="n"/>
+      <c r="P66" s="25" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -6677,18 +6518,18 @@
           <t>Disconnect counts in this class</t>
         </is>
       </c>
-      <c r="E67" s="27" t="n"/>
-      <c r="F67" s="27" t="n"/>
-      <c r="G67" s="27" t="n"/>
-      <c r="H67" s="27" t="n"/>
-      <c r="I67" s="27" t="n"/>
-      <c r="J67" s="27" t="n"/>
-      <c r="K67" s="27" t="n"/>
-      <c r="L67" s="27" t="n"/>
-      <c r="M67" s="27" t="n"/>
-      <c r="N67" s="27" t="n"/>
-      <c r="O67" s="27" t="n"/>
-      <c r="P67" s="27" t="n"/>
+      <c r="E67" s="25" t="n"/>
+      <c r="F67" s="25" t="n"/>
+      <c r="G67" s="25" t="n"/>
+      <c r="H67" s="25" t="n"/>
+      <c r="I67" s="25" t="n"/>
+      <c r="J67" s="25" t="n"/>
+      <c r="K67" s="25" t="n"/>
+      <c r="L67" s="25" t="n"/>
+      <c r="M67" s="25" t="n"/>
+      <c r="N67" s="25" t="n"/>
+      <c r="O67" s="25" t="n"/>
+      <c r="P67" s="25" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -6711,18 +6552,18 @@
           <t>Disconnect counts in this class</t>
         </is>
       </c>
-      <c r="E68" s="27" t="n"/>
-      <c r="F68" s="27" t="n"/>
-      <c r="G68" s="27" t="n"/>
-      <c r="H68" s="27" t="n"/>
-      <c r="I68" s="27" t="n"/>
-      <c r="J68" s="27" t="n"/>
-      <c r="K68" s="27" t="n"/>
-      <c r="L68" s="27" t="n"/>
-      <c r="M68" s="27" t="n"/>
-      <c r="N68" s="27" t="n"/>
-      <c r="O68" s="27" t="n"/>
-      <c r="P68" s="27" t="n"/>
+      <c r="E68" s="25" t="n"/>
+      <c r="F68" s="25" t="n"/>
+      <c r="G68" s="25" t="n"/>
+      <c r="H68" s="25" t="n"/>
+      <c r="I68" s="25" t="n"/>
+      <c r="J68" s="25" t="n"/>
+      <c r="K68" s="25" t="n"/>
+      <c r="L68" s="25" t="n"/>
+      <c r="M68" s="25" t="n"/>
+      <c r="N68" s="25" t="n"/>
+      <c r="O68" s="25" t="n"/>
+      <c r="P68" s="25" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -6745,18 +6586,18 @@
           <t>Disconnect counts in this class</t>
         </is>
       </c>
-      <c r="E69" s="27" t="n"/>
-      <c r="F69" s="27" t="n"/>
-      <c r="G69" s="27" t="n"/>
-      <c r="H69" s="27" t="n"/>
-      <c r="I69" s="27" t="n"/>
-      <c r="J69" s="27" t="n"/>
-      <c r="K69" s="27" t="n"/>
-      <c r="L69" s="27" t="n"/>
-      <c r="M69" s="27" t="n"/>
-      <c r="N69" s="27" t="n"/>
-      <c r="O69" s="27" t="n"/>
-      <c r="P69" s="27" t="n"/>
+      <c r="E69" s="25" t="n"/>
+      <c r="F69" s="25" t="n"/>
+      <c r="G69" s="25" t="n"/>
+      <c r="H69" s="25" t="n"/>
+      <c r="I69" s="25" t="n"/>
+      <c r="J69" s="25" t="n"/>
+      <c r="K69" s="25" t="n"/>
+      <c r="L69" s="25" t="n"/>
+      <c r="M69" s="25" t="n"/>
+      <c r="N69" s="25" t="n"/>
+      <c r="O69" s="25" t="n"/>
+      <c r="P69" s="25" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -6779,18 +6620,18 @@
           <t>Needed for rate vs control (pptx slide 4 validation)</t>
         </is>
       </c>
-      <c r="E70" s="27" t="n"/>
-      <c r="F70" s="27" t="n"/>
-      <c r="G70" s="27" t="n"/>
-      <c r="H70" s="27" t="n"/>
-      <c r="I70" s="27" t="n"/>
-      <c r="J70" s="27" t="n"/>
-      <c r="K70" s="27" t="n"/>
-      <c r="L70" s="27" t="n"/>
-      <c r="M70" s="27" t="n"/>
-      <c r="N70" s="27" t="n"/>
-      <c r="O70" s="27" t="n"/>
-      <c r="P70" s="27" t="n"/>
+      <c r="E70" s="25" t="n"/>
+      <c r="F70" s="25" t="n"/>
+      <c r="G70" s="25" t="n"/>
+      <c r="H70" s="25" t="n"/>
+      <c r="I70" s="25" t="n"/>
+      <c r="J70" s="25" t="n"/>
+      <c r="K70" s="25" t="n"/>
+      <c r="L70" s="25" t="n"/>
+      <c r="M70" s="25" t="n"/>
+      <c r="N70" s="25" t="n"/>
+      <c r="O70" s="25" t="n"/>
+      <c r="P70" s="25" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -6813,18 +6654,18 @@
           <t>Optional — rate = disconnects / begin</t>
         </is>
       </c>
-      <c r="E71" s="27" t="n"/>
-      <c r="F71" s="27" t="n"/>
-      <c r="G71" s="27" t="n"/>
-      <c r="H71" s="27" t="n"/>
-      <c r="I71" s="27" t="n"/>
-      <c r="J71" s="27" t="n"/>
-      <c r="K71" s="27" t="n"/>
-      <c r="L71" s="27" t="n"/>
-      <c r="M71" s="27" t="n"/>
-      <c r="N71" s="27" t="n"/>
-      <c r="O71" s="27" t="n"/>
-      <c r="P71" s="27" t="n"/>
+      <c r="E71" s="25" t="n"/>
+      <c r="F71" s="25" t="n"/>
+      <c r="G71" s="25" t="n"/>
+      <c r="H71" s="25" t="n"/>
+      <c r="I71" s="25" t="n"/>
+      <c r="J71" s="25" t="n"/>
+      <c r="K71" s="25" t="n"/>
+      <c r="L71" s="25" t="n"/>
+      <c r="M71" s="25" t="n"/>
+      <c r="N71" s="25" t="n"/>
+      <c r="O71" s="25" t="n"/>
+      <c r="P71" s="25" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -6847,18 +6688,18 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E72" s="27" t="n"/>
-      <c r="F72" s="27" t="n"/>
-      <c r="G72" s="27" t="n"/>
-      <c r="H72" s="27" t="n"/>
-      <c r="I72" s="27" t="n"/>
-      <c r="J72" s="27" t="n"/>
-      <c r="K72" s="27" t="n"/>
-      <c r="L72" s="27" t="n"/>
-      <c r="M72" s="27" t="n"/>
-      <c r="N72" s="27" t="n"/>
-      <c r="O72" s="27" t="n"/>
-      <c r="P72" s="27" t="n"/>
+      <c r="E72" s="25" t="n"/>
+      <c r="F72" s="25" t="n"/>
+      <c r="G72" s="25" t="n"/>
+      <c r="H72" s="25" t="n"/>
+      <c r="I72" s="25" t="n"/>
+      <c r="J72" s="25" t="n"/>
+      <c r="K72" s="25" t="n"/>
+      <c r="L72" s="25" t="n"/>
+      <c r="M72" s="25" t="n"/>
+      <c r="N72" s="25" t="n"/>
+      <c r="O72" s="25" t="n"/>
+      <c r="P72" s="25" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -6881,18 +6722,18 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E73" s="27" t="n"/>
-      <c r="F73" s="27" t="n"/>
-      <c r="G73" s="27" t="n"/>
-      <c r="H73" s="27" t="n"/>
-      <c r="I73" s="27" t="n"/>
-      <c r="J73" s="27" t="n"/>
-      <c r="K73" s="27" t="n"/>
-      <c r="L73" s="27" t="n"/>
-      <c r="M73" s="27" t="n"/>
-      <c r="N73" s="27" t="n"/>
-      <c r="O73" s="27" t="n"/>
-      <c r="P73" s="27" t="n"/>
+      <c r="E73" s="25" t="n"/>
+      <c r="F73" s="25" t="n"/>
+      <c r="G73" s="25" t="n"/>
+      <c r="H73" s="25" t="n"/>
+      <c r="I73" s="25" t="n"/>
+      <c r="J73" s="25" t="n"/>
+      <c r="K73" s="25" t="n"/>
+      <c r="L73" s="25" t="n"/>
+      <c r="M73" s="25" t="n"/>
+      <c r="N73" s="25" t="n"/>
+      <c r="O73" s="25" t="n"/>
+      <c r="P73" s="25" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
@@ -6938,18 +6779,18 @@
         </is>
       </c>
       <c r="B77" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$66:$P$66,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$66:$P$66,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$66:$P$66,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="C77" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$71:$P$71,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D77" s="30">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$71:$P$71,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$71:$P$71,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
+        <v/>
+      </c>
+      <c r="D77" s="28">
         <f>IF(OR(B77="",C77="",C77=0),"",B77/C77)</f>
         <v/>
       </c>
-      <c r="E77" s="31">
+      <c r="E77" s="29">
         <f>IF(OR(D77="",$D$80=""),"",D77/$D$80)</f>
         <v/>
       </c>
@@ -6961,18 +6802,18 @@
         </is>
       </c>
       <c r="B78" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$67:$P$67,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$67:$P$67,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$67:$P$67,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="C78" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$72:$P$72,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D78" s="30">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$72:$P$72,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$72:$P$72,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="28">
         <f>IF(OR(B78="",C78="",C78=0),"",B78/C78)</f>
         <v/>
       </c>
-      <c r="E78" s="31">
+      <c r="E78" s="29">
         <f>IF(OR(D78="",$D$80=""),"",D78/$D$80)</f>
         <v/>
       </c>
@@ -6984,18 +6825,18 @@
         </is>
       </c>
       <c r="B79" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$68:$P$68,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$68:$P$68,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$68:$P$68,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="C79" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$73:$P$73,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="30">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$73:$P$73,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$73:$P$73,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="28">
         <f>IF(OR(B79="",C79="",C79=0),"",B79/C79)</f>
         <v/>
       </c>
-      <c r="E79" s="31">
+      <c r="E79" s="29">
         <f>IF(OR(D79="",$D$80=""),"",D79/$D$80)</f>
         <v/>
       </c>
@@ -7007,18 +6848,18 @@
         </is>
       </c>
       <c r="B80" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$69:$P$69,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$69:$P$69,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$69:$P$69,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="C80" s="14">
-        <f>IFERROR(INDEX('Attribution'!$E$70:$P$70,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="30">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Attribution'!$E$70:$P$70,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0)))=1,"",INDEX('Attribution'!$E$70:$P$70,MATCH(Param_Quarter,'Attribution'!$E$5:$P$5,0))),"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="28">
         <f>IF(OR(B80="",C80="",C80=0),"",B80/C80)</f>
         <v/>
       </c>
-      <c r="E80" s="31">
+      <c r="E80" s="29">
         <f>IF(OR(D80="",$D$80=""),"",D80/$D$80)</f>
         <v/>
       </c>
@@ -7039,11 +6880,11 @@
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="10">
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A2:L3"/>
-    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A63:H63"/>
     <mergeCell ref="A64:H64"/>
@@ -7110,31 +6951,31 @@
           <t>PPTX: tenure · ARPU tier · exposure class (on Attribution) · rural as Scenario 3 (satellite/low-density). G1 / six-recommendation-areas also require: core vs rural Internet; AT&amp;T ~27% / Verizon ~16% overlap vs rest (those shares are footprint mix, not losses); product mix at leave; sampled exit signal. Yellow = INPUT counts of disconnects (or net adds if labeled). Blank = not tracked.</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="16" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="17" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n"/>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="n"/>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="21" t="n"/>
-      <c r="I3" s="21" t="n"/>
-      <c r="J3" s="21" t="n"/>
-      <c r="K3" s="21" t="n"/>
-      <c r="L3" s="22" t="n"/>
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="23" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -7253,18 +7094,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="25" t="n"/>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="25" t="n"/>
+      <c r="L7" s="25" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="25" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -7287,18 +7128,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="27" t="n"/>
-      <c r="O8" s="27" t="n"/>
-      <c r="P8" s="27" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="L8" s="25" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="25" t="n"/>
+      <c r="O8" s="25" t="n"/>
+      <c r="P8" s="25" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -7321,18 +7162,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="27" t="n"/>
-      <c r="J9" s="27" t="n"/>
-      <c r="K9" s="27" t="n"/>
-      <c r="L9" s="27" t="n"/>
-      <c r="M9" s="27" t="n"/>
-      <c r="N9" s="27" t="n"/>
-      <c r="O9" s="27" t="n"/>
-      <c r="P9" s="27" t="n"/>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="25" t="n"/>
+      <c r="L9" s="25" t="n"/>
+      <c r="M9" s="25" t="n"/>
+      <c r="N9" s="25" t="n"/>
+      <c r="O9" s="25" t="n"/>
+      <c r="P9" s="25" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -7355,18 +7196,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="27" t="n"/>
-      <c r="M10" s="27" t="n"/>
-      <c r="N10" s="27" t="n"/>
-      <c r="O10" s="27" t="n"/>
-      <c r="P10" s="27" t="n"/>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="25" t="n"/>
+      <c r="L10" s="25" t="n"/>
+      <c r="M10" s="25" t="n"/>
+      <c r="N10" s="25" t="n"/>
+      <c r="O10" s="25" t="n"/>
+      <c r="P10" s="25" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -7389,18 +7230,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-      <c r="O11" s="27" t="n"/>
-      <c r="P11" s="27" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="25" t="n"/>
+      <c r="L11" s="25" t="n"/>
+      <c r="M11" s="25" t="n"/>
+      <c r="N11" s="25" t="n"/>
+      <c r="O11" s="25" t="n"/>
+      <c r="P11" s="25" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -7585,18 +7426,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
-      <c r="H16" s="27" t="n"/>
-      <c r="I16" s="27" t="n"/>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="27" t="n"/>
-      <c r="M16" s="27" t="n"/>
-      <c r="N16" s="27" t="n"/>
-      <c r="O16" s="27" t="n"/>
-      <c r="P16" s="27" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="25" t="n"/>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="25" t="n"/>
+      <c r="O16" s="25" t="n"/>
+      <c r="P16" s="25" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -7619,18 +7460,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="27" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="27" t="n"/>
-      <c r="O17" s="27" t="n"/>
-      <c r="P17" s="27" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="25" t="n"/>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="25" t="n"/>
+      <c r="O17" s="25" t="n"/>
+      <c r="P17" s="25" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -7653,18 +7494,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="n"/>
-      <c r="I18" s="27" t="n"/>
-      <c r="J18" s="27" t="n"/>
-      <c r="K18" s="27" t="n"/>
-      <c r="L18" s="27" t="n"/>
-      <c r="M18" s="27" t="n"/>
-      <c r="N18" s="27" t="n"/>
-      <c r="O18" s="27" t="n"/>
-      <c r="P18" s="27" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="25" t="n"/>
+      <c r="M18" s="25" t="n"/>
+      <c r="N18" s="25" t="n"/>
+      <c r="O18" s="25" t="n"/>
+      <c r="P18" s="25" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -7849,18 +7690,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
-      <c r="H23" s="27" t="n"/>
-      <c r="I23" s="27" t="n"/>
-      <c r="J23" s="27" t="n"/>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="27" t="n"/>
-      <c r="M23" s="27" t="n"/>
-      <c r="N23" s="27" t="n"/>
-      <c r="O23" s="27" t="n"/>
-      <c r="P23" s="27" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="25" t="n"/>
+      <c r="M23" s="25" t="n"/>
+      <c r="N23" s="25" t="n"/>
+      <c r="O23" s="25" t="n"/>
+      <c r="P23" s="25" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -7883,18 +7724,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
-      <c r="H24" s="27" t="n"/>
-      <c r="I24" s="27" t="n"/>
-      <c r="J24" s="27" t="n"/>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="27" t="n"/>
-      <c r="M24" s="27" t="n"/>
-      <c r="N24" s="27" t="n"/>
-      <c r="O24" s="27" t="n"/>
-      <c r="P24" s="27" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="25" t="n"/>
+      <c r="N24" s="25" t="n"/>
+      <c r="O24" s="25" t="n"/>
+      <c r="P24" s="25" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -7917,18 +7758,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
-      <c r="H25" s="27" t="n"/>
-      <c r="I25" s="27" t="n"/>
-      <c r="J25" s="27" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="27" t="n"/>
-      <c r="M25" s="27" t="n"/>
-      <c r="N25" s="27" t="n"/>
-      <c r="O25" s="27" t="n"/>
-      <c r="P25" s="27" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="25" t="n"/>
+      <c r="N25" s="25" t="n"/>
+      <c r="O25" s="25" t="n"/>
+      <c r="P25" s="25" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -7951,18 +7792,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
-      <c r="H26" s="27" t="n"/>
-      <c r="I26" s="27" t="n"/>
-      <c r="J26" s="27" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="27" t="n"/>
-      <c r="M26" s="27" t="n"/>
-      <c r="N26" s="27" t="n"/>
-      <c r="O26" s="27" t="n"/>
-      <c r="P26" s="27" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="25" t="n"/>
+      <c r="N26" s="25" t="n"/>
+      <c r="O26" s="25" t="n"/>
+      <c r="P26" s="25" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -8147,18 +7988,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="27" t="n"/>
-      <c r="H31" s="27" t="n"/>
-      <c r="I31" s="27" t="n"/>
-      <c r="J31" s="27" t="n"/>
-      <c r="K31" s="27" t="n"/>
-      <c r="L31" s="27" t="n"/>
-      <c r="M31" s="27" t="n"/>
-      <c r="N31" s="27" t="n"/>
-      <c r="O31" s="27" t="n"/>
-      <c r="P31" s="27" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="25" t="n"/>
+      <c r="L31" s="25" t="n"/>
+      <c r="M31" s="25" t="n"/>
+      <c r="N31" s="25" t="n"/>
+      <c r="O31" s="25" t="n"/>
+      <c r="P31" s="25" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -8181,18 +8022,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="27" t="n"/>
-      <c r="H32" s="27" t="n"/>
-      <c r="I32" s="27" t="n"/>
-      <c r="J32" s="27" t="n"/>
-      <c r="K32" s="27" t="n"/>
-      <c r="L32" s="27" t="n"/>
-      <c r="M32" s="27" t="n"/>
-      <c r="N32" s="27" t="n"/>
-      <c r="O32" s="27" t="n"/>
-      <c r="P32" s="27" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="25" t="n"/>
+      <c r="M32" s="25" t="n"/>
+      <c r="N32" s="25" t="n"/>
+      <c r="O32" s="25" t="n"/>
+      <c r="P32" s="25" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -8215,18 +8056,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="27" t="n"/>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="25" t="n"/>
+      <c r="G33" s="25" t="n"/>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="25" t="n"/>
+      <c r="L33" s="25" t="n"/>
+      <c r="M33" s="25" t="n"/>
+      <c r="N33" s="25" t="n"/>
+      <c r="O33" s="25" t="n"/>
+      <c r="P33" s="25" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
@@ -8411,18 +8252,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
-      <c r="H38" s="27" t="n"/>
-      <c r="I38" s="27" t="n"/>
-      <c r="J38" s="27" t="n"/>
-      <c r="K38" s="27" t="n"/>
-      <c r="L38" s="27" t="n"/>
-      <c r="M38" s="27" t="n"/>
-      <c r="N38" s="27" t="n"/>
-      <c r="O38" s="27" t="n"/>
-      <c r="P38" s="27" t="n"/>
+      <c r="E38" s="25" t="n"/>
+      <c r="F38" s="25" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="25" t="n"/>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="25" t="n"/>
+      <c r="L38" s="25" t="n"/>
+      <c r="M38" s="25" t="n"/>
+      <c r="N38" s="25" t="n"/>
+      <c r="O38" s="25" t="n"/>
+      <c r="P38" s="25" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -8445,18 +8286,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
-      <c r="H39" s="27" t="n"/>
-      <c r="I39" s="27" t="n"/>
-      <c r="J39" s="27" t="n"/>
-      <c r="K39" s="27" t="n"/>
-      <c r="L39" s="27" t="n"/>
-      <c r="M39" s="27" t="n"/>
-      <c r="N39" s="27" t="n"/>
-      <c r="O39" s="27" t="n"/>
-      <c r="P39" s="27" t="n"/>
+      <c r="E39" s="25" t="n"/>
+      <c r="F39" s="25" t="n"/>
+      <c r="G39" s="25" t="n"/>
+      <c r="H39" s="25" t="n"/>
+      <c r="I39" s="25" t="n"/>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="25" t="n"/>
+      <c r="L39" s="25" t="n"/>
+      <c r="M39" s="25" t="n"/>
+      <c r="N39" s="25" t="n"/>
+      <c r="O39" s="25" t="n"/>
+      <c r="P39" s="25" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -8479,18 +8320,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="27" t="n"/>
-      <c r="H40" s="27" t="n"/>
-      <c r="I40" s="27" t="n"/>
-      <c r="J40" s="27" t="n"/>
-      <c r="K40" s="27" t="n"/>
-      <c r="L40" s="27" t="n"/>
-      <c r="M40" s="27" t="n"/>
-      <c r="N40" s="27" t="n"/>
-      <c r="O40" s="27" t="n"/>
-      <c r="P40" s="27" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="25" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="25" t="n"/>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="25" t="n"/>
+      <c r="L40" s="25" t="n"/>
+      <c r="M40" s="25" t="n"/>
+      <c r="N40" s="25" t="n"/>
+      <c r="O40" s="25" t="n"/>
+      <c r="P40" s="25" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -8513,18 +8354,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
-      <c r="H41" s="27" t="n"/>
-      <c r="I41" s="27" t="n"/>
-      <c r="J41" s="27" t="n"/>
-      <c r="K41" s="27" t="n"/>
-      <c r="L41" s="27" t="n"/>
-      <c r="M41" s="27" t="n"/>
-      <c r="N41" s="27" t="n"/>
-      <c r="O41" s="27" t="n"/>
-      <c r="P41" s="27" t="n"/>
+      <c r="E41" s="25" t="n"/>
+      <c r="F41" s="25" t="n"/>
+      <c r="G41" s="25" t="n"/>
+      <c r="H41" s="25" t="n"/>
+      <c r="I41" s="25" t="n"/>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="25" t="n"/>
+      <c r="L41" s="25" t="n"/>
+      <c r="M41" s="25" t="n"/>
+      <c r="N41" s="25" t="n"/>
+      <c r="O41" s="25" t="n"/>
+      <c r="P41" s="25" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -8547,18 +8388,18 @@
           <t>Disconnect counts</t>
         </is>
       </c>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="27" t="n"/>
-      <c r="H42" s="27" t="n"/>
-      <c r="I42" s="27" t="n"/>
-      <c r="J42" s="27" t="n"/>
-      <c r="K42" s="27" t="n"/>
-      <c r="L42" s="27" t="n"/>
-      <c r="M42" s="27" t="n"/>
-      <c r="N42" s="27" t="n"/>
-      <c r="O42" s="27" t="n"/>
-      <c r="P42" s="27" t="n"/>
+      <c r="E42" s="25" t="n"/>
+      <c r="F42" s="25" t="n"/>
+      <c r="G42" s="25" t="n"/>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="25" t="n"/>
+      <c r="L42" s="25" t="n"/>
+      <c r="M42" s="25" t="n"/>
+      <c r="N42" s="25" t="n"/>
+      <c r="O42" s="25" t="n"/>
+      <c r="P42" s="25" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
@@ -8739,18 +8580,18 @@
           <t>Needed for a rate, not just a share</t>
         </is>
       </c>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="27" t="n"/>
-      <c r="J47" s="27" t="n"/>
-      <c r="K47" s="27" t="n"/>
-      <c r="L47" s="27" t="n"/>
-      <c r="M47" s="27" t="n"/>
-      <c r="N47" s="27" t="n"/>
-      <c r="O47" s="27" t="n"/>
-      <c r="P47" s="27" t="n"/>
+      <c r="E47" s="25" t="n"/>
+      <c r="F47" s="25" t="n"/>
+      <c r="G47" s="25" t="n"/>
+      <c r="H47" s="25" t="n"/>
+      <c r="I47" s="25" t="n"/>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="25" t="n"/>
+      <c r="L47" s="25" t="n"/>
+      <c r="M47" s="25" t="n"/>
+      <c r="N47" s="25" t="n"/>
+      <c r="O47" s="25" t="n"/>
+      <c r="P47" s="25" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -8773,18 +8614,18 @@
           <t>Needed for a rate, not just a share</t>
         </is>
       </c>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="27" t="n"/>
-      <c r="G48" s="27" t="n"/>
-      <c r="H48" s="27" t="n"/>
-      <c r="I48" s="27" t="n"/>
-      <c r="J48" s="27" t="n"/>
-      <c r="K48" s="27" t="n"/>
-      <c r="L48" s="27" t="n"/>
-      <c r="M48" s="27" t="n"/>
-      <c r="N48" s="27" t="n"/>
-      <c r="O48" s="27" t="n"/>
-      <c r="P48" s="27" t="n"/>
+      <c r="E48" s="25" t="n"/>
+      <c r="F48" s="25" t="n"/>
+      <c r="G48" s="25" t="n"/>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="25" t="n"/>
+      <c r="L48" s="25" t="n"/>
+      <c r="M48" s="25" t="n"/>
+      <c r="N48" s="25" t="n"/>
+      <c r="O48" s="25" t="n"/>
+      <c r="P48" s="25" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -8854,7 +8695,7 @@
         </is>
       </c>
       <c r="C53" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$7:$P$7,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$7:$P$7,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$7:$P$7,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D53" s="15">
@@ -8862,14 +8703,14 @@
         <v/>
       </c>
       <c r="E53" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$47:$P$47,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="30">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$47:$P$47,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$47:$P$47,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="28">
         <f>IF(OR(C53="",E53="",E53=0),"",C53/E53)</f>
         <v/>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="29">
         <f>IF(OR(F53="",'Net-loss tracker'!B43=""),"",F53/'Net-loss tracker'!B43)</f>
         <v/>
       </c>
@@ -8890,7 +8731,7 @@
         </is>
       </c>
       <c r="C54" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$8:$P$8,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$8:$P$8,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$8:$P$8,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D54" s="15">
@@ -8898,14 +8739,14 @@
         <v/>
       </c>
       <c r="E54" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$48:$P$48,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F54" s="30">
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$48:$P$48,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$48:$P$48,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="28">
         <f>IF(OR(C54="",E54="",E54=0),"",C54/E54)</f>
         <v/>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="29">
         <f>IF(OR(F54="",'Net-loss tracker'!B43=""),"",F54/'Net-loss tracker'!B43)</f>
         <v/>
       </c>
@@ -8926,7 +8767,7 @@
         </is>
       </c>
       <c r="C55" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$9:$P$9,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$9:$P$9,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$9:$P$9,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D55" s="15">
@@ -8934,11 +8775,11 @@
         <v/>
       </c>
       <c r="E55" s="12" t="inlineStr"/>
-      <c r="F55" s="30">
+      <c r="F55" s="28">
         <f>IF(OR(C55="",E55="",E55=0),"",C55/E55)</f>
         <v/>
       </c>
-      <c r="G55" s="31">
+      <c r="G55" s="29">
         <f>IF(OR(F55="",'Net-loss tracker'!B43=""),"",F55/'Net-loss tracker'!B43)</f>
         <v/>
       </c>
@@ -8959,7 +8800,7 @@
         </is>
       </c>
       <c r="C56" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$10:$P$10,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$10:$P$10,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$10:$P$10,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D56" s="15">
@@ -8967,11 +8808,11 @@
         <v/>
       </c>
       <c r="E56" s="12" t="inlineStr"/>
-      <c r="F56" s="30">
+      <c r="F56" s="28">
         <f>IF(OR(C56="",E56="",E56=0),"",C56/E56)</f>
         <v/>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="29">
         <f>IF(OR(F56="",'Net-loss tracker'!B43=""),"",F56/'Net-loss tracker'!B43)</f>
         <v/>
       </c>
@@ -8992,7 +8833,7 @@
         </is>
       </c>
       <c r="C57" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$11:$P$11,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$11:$P$11,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$11:$P$11,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D57" s="15">
@@ -9000,11 +8841,11 @@
         <v/>
       </c>
       <c r="E57" s="12" t="inlineStr"/>
-      <c r="F57" s="30">
+      <c r="F57" s="28">
         <f>IF(OR(C57="",E57="",E57=0),"",C57/E57)</f>
         <v/>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="29">
         <f>IF(OR(F57="",'Net-loss tracker'!B43=""),"",F57/'Net-loss tracker'!B43)</f>
         <v/>
       </c>
@@ -9047,7 +8888,7 @@
         </is>
       </c>
       <c r="C60" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$16:$P$16,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$16:$P$16,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$16:$P$16,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D60" s="15">
@@ -9067,7 +8908,7 @@
         </is>
       </c>
       <c r="C61" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$17:$P$17,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$17:$P$17,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$17:$P$17,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D61" s="15">
@@ -9087,7 +8928,7 @@
         </is>
       </c>
       <c r="C62" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$18:$P$18,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$18:$P$18,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$18:$P$18,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D62" s="15">
@@ -9129,7 +8970,7 @@
         </is>
       </c>
       <c r="C65" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$23:$P$23,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$23:$P$23,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$23:$P$23,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D65" s="15">
@@ -9149,7 +8990,7 @@
         </is>
       </c>
       <c r="C66" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$24:$P$24,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$24:$P$24,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$24:$P$24,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D66" s="15">
@@ -9169,7 +9010,7 @@
         </is>
       </c>
       <c r="C67" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$25:$P$25,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$25:$P$25,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$25:$P$25,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D67" s="15">
@@ -9189,7 +9030,7 @@
         </is>
       </c>
       <c r="C68" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$26:$P$26,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$26:$P$26,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$26:$P$26,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D68" s="15">
@@ -9231,7 +9072,7 @@
         </is>
       </c>
       <c r="C71" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$38:$P$38,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$38:$P$38,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$38:$P$38,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D71" s="15">
@@ -9251,7 +9092,7 @@
         </is>
       </c>
       <c r="C72" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$39:$P$39,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$39:$P$39,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$39:$P$39,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D72" s="15">
@@ -9271,7 +9112,7 @@
         </is>
       </c>
       <c r="C73" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$40:$P$40,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$40:$P$40,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$40:$P$40,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D73" s="15">
@@ -9291,7 +9132,7 @@
         </is>
       </c>
       <c r="C74" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$41:$P$41,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$41:$P$41,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$41:$P$41,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D74" s="15">
@@ -9311,7 +9152,7 @@
         </is>
       </c>
       <c r="C75" s="14">
-        <f>IFERROR(INDEX('Segments'!$E$42:$P$42,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)),"")</f>
+        <f>IFERROR(IF(COUNTBLANK(INDEX('Segments'!$E$42:$P$42,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0)))=1,"",INDEX('Segments'!$E$42:$P$42,MATCH(Param_Quarter,'Segments'!$E$5:$P$5,0))),"")</f>
         <v/>
       </c>
       <c r="D75" s="15">
@@ -9538,17 +9379,17 @@
           <t>Yellow = INPUT. Blue fill = ESTIMATED template default the user can change. PPTX slide 5: ≥40% dominant · 25–40% mixed · &lt;25% null. FWA signal &gt;35–40%. Thresholds are judgment calls, set in advance (pptx notes: arbitrary-but-stated beats unstated).</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="17" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="20" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="20" t="n"/>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="22" t="n"/>
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="23" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
@@ -9588,7 +9429,7 @@
           <t>Selected quarter</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
@@ -9615,9 +9456,9 @@
           <t>Reason taxonomy</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>PPTX 6-scenario</t>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>GAP R1–R4 only</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -9627,7 +9468,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>PPTX scenarios 1–6. Alternate label only — codes stay R1–R4 + satellite + residual.</t>
+          <t>Dashboard router is GAP R1–R4 (decisions.md / six-recommendation-areas). PPTX S1–S6 stays on the Playbook sheet as reference only.</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9483,7 @@
           <t>Highlight color (tables)</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>2E75B6</t>
         </is>
@@ -9669,7 +9510,7 @@
           <t>Dominant-driver threshold</t>
         </is>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="31" t="n">
         <v>0.4</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -9694,7 +9535,7 @@
           <t>Mixed-picture floor</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="31" t="n">
         <v>0.25</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -9719,7 +9560,7 @@
           <t>FWA scenario trigger</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="31" t="n">
         <v>0.35</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -9744,7 +9585,7 @@
           <t>Fiber scenario trigger</t>
         </is>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="31" t="n">
         <v>0.4</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -9769,7 +9610,7 @@
           <t>Satellite scenario trigger</t>
         </is>
       </c>
-      <c r="C12" s="33" t="n">
+      <c r="C12" s="31" t="n">
         <v>0.25</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -9794,7 +9635,7 @@
           <t>Co-equal band (pp of mix)</t>
         </is>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="31" t="n">
         <v>0.05</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -9819,7 +9660,7 @@
           <t>Core-drives-print share</t>
         </is>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="31" t="n">
         <v>0.7</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -9844,7 +9685,7 @@
           <t>Segment rate-skew vs company</t>
         </is>
       </c>
-      <c r="C15" s="34" t="n">
+      <c r="C15" s="32" t="n">
         <v>1.5</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -9869,7 +9710,7 @@
           <t>Require two consecutive quarters before full-scale?</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -9896,7 +9737,7 @@
           <t>Tracker already exists and is used quarterly?</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>No — fill G1 first</t>
         </is>
@@ -9923,7 +9764,7 @@
           <t>Use Comcast benchmark?</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -9950,7 +9791,7 @@
           <t>Attribution input mode</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>Counts</t>
         </is>
@@ -9962,7 +9803,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Counts (preferred) = sampled disconnects. Percent allocates the selected base — not a measured rate.</t>
+          <t>Counts only. Percent mode was removed — allocating |print| is not a measured mix and cannot fire a scaled play.</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9815,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>If only % is filled, allocate against</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr">
-        <is>
-          <t>Disconnects (if known), else |public print|</t>
+          <t>If only % is offered</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>Reject — Counts required to fire</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -9989,7 +9830,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Playbook: do not invent a mix. Allocating the net print is a PLACEHOLDER, not a churn rate.</t>
+          <t>Do not allocate the public print as a fake mix. Paste sampled disconnect COUNTS (T3 + A1–A6).</t>
         </is>
       </c>
     </row>
@@ -10004,7 +9845,7 @@
           <t>Material share of peer excess</t>
         </is>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C21" s="31" t="n">
         <v>0.25</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -10029,7 +9870,7 @@
           <t>Playbook committed excess (customers)</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n">
+      <c r="C22" s="34" t="n">
         <v>54000</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -10088,14 +9929,14 @@
           <t>R-FWA</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Competitive FWA</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>S1 FWA-driven</t>
+          <t>S1 FWA-driven (ref)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -10105,7 +9946,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Convergence pricing / FWA-match in FWA zones; economics gate on MVNO unit cost.</t>
+          <t>GAP: 12-month rate-lock on and off overlap; hand on-overlap FWA to fiber if it is a stepping-stone.</t>
         </is>
       </c>
     </row>
@@ -10115,14 +9956,14 @@
           <t>R-FIB</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Competitive fiber (overbuild)</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>S2 Fiber-driven</t>
+          <t>S2 Fiber-driven (ref)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -10132,7 +9973,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Re-sequence DOCSIS 4.0 by exposure + symmetric win-back. Node-split only if sample names speed.</t>
+          <t>GAP: overlap-zip gig/symmetry; node-split only if the sample names speed. Off-overlap is the wrong play (W4).</t>
         </is>
       </c>
     </row>
@@ -10142,14 +9983,14 @@
           <t>R-SAT</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>LEO satellite</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>S3 Satellite-driven</t>
+          <t>S3 Satellite-driven (ref)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -10159,7 +10000,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Accelerate rural subsidized activation ahead of Starlink/Kuiper. Honor RDOF/BEAD.</t>
+          <t>Not a GAP spend program this quarter. WHERE overlay only — do not fire as R1–R4.</t>
         </is>
       </c>
     </row>
@@ -10169,14 +10010,14 @@
           <t>R-MOV</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Move-out / housing</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>S4 Housing-driven</t>
+          <t>S4 Housing-driven (ref)</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -10186,7 +10027,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Mover capture: Community Solutions / MDU / instant-on. Not a save-offer problem.</t>
+          <t>GAP: TOS/MDU / instant-on for 6 months. Cheaper lever first. Not a save-offer problem.</t>
         </is>
       </c>
     </row>
@@ -10196,14 +10037,14 @@
           <t>R-NPY</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Non-pay / economic</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>S5 Non-pay</t>
+          <t>S5 Non-pay (ref)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -10213,7 +10054,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Payment arrangement / value tier at delinquency. Funded by care opex if this is the leak.</t>
+          <t>GAP: payment arrangement / 90-day first-bill save. Funded by care opex if this is the leak.</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10064,7 @@
           <t>R-OTH</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Service / other</t>
         </is>
@@ -10240,7 +10081,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Unmapped residual. If this is largest, the sample is incomplete — do not fire a plant program.</t>
+          <t>Unmapped residual. If this is largest or ≥2% of base, HOLD — do not fire a plant program.</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10118,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>PPTX 6-scenario</t>
+          <t>GAP R1–R4 only</t>
         </is>
       </c>
     </row>
@@ -10297,14 +10138,9 @@
           <t>No — fill G1 first</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>GAP R1–R4 only</t>
+          <t>PPTX 6-scenario (Playbook ref only)</t>
         </is>
       </c>
     </row>
@@ -10385,17 +10221,17 @@
           <t>Comcast Q1 2026 residential broadband −65,000 and begin 28,719,000 are RETRIEVED (CMCSA Ex99.1; network_churn_model.py). Other Comcast quarters stay INPUT. 54,000 is the playbook commit (round down from 54.4k) — cite six-recommendation-areas.md, not the pptx.</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="17" t="n"/>
+      <c r="B47" s="19" t="n"/>
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="19" t="n"/>
+      <c r="E47" s="20" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="20" t="n"/>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="22" t="n"/>
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="22" t="n"/>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="23" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1"/>
   </sheetData>
@@ -10418,7 +10254,7 @@
       <formula1>$B$34:$B$35</formula1>
     </dataValidation>
     <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>$D$34:$D$35</formula1>
+      <formula1>$D$34:$D$34</formula1>
     </dataValidation>
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>$E$34:$E$35</formula1>
@@ -10474,19 +10310,19 @@
           <t>Solving playbook: one assumption per line with a line ID; derived lines are formulas. Tag every input RETRIEVED or INPUT (user-entered). Thresholds are ESTIMATED template defaults. Dollar-weight is not meaningful until Attribution is filled — then the mix is 100% INPUT.</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="17" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n"/>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="n"/>
-      <c r="F3" s="22" t="n"/>
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="23" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -10662,9 +10498,10 @@
           <t>T2 - T3</t>
         </is>
       </c>
-      <c r="F9" s="5">
-        <f>gross-disconnects</f>
-        <v/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>T2 − T3</t>
+        </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -11840,7 +11677,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PLAYBOOK ON A PAGE  ·  reference only — does not fire from empty cells</t>
+          <t>PLAYBOOK ON A PAGE  ·  PPTX S1–S6 REFERENCE ONLY — Dashboard fires GAP R1–R4</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11853,24 +11690,24 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>PPTX slides 6-9 (scenarios 1-6) plus GAP R1-R4 / WHERE overlays from decisions.md. Budgets and owners are pre-authorized in the deck, not sized here. Dashboard routes a scenario; this sheet is the leave-behind.</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="17" t="n"/>
+          <t>Dashboard GAP R1–R4 is the rec in force (TOS/MDU, FWA rate-lock, overlap gig/symmetry, first-bill save). This sheet is the pptx leave-behind. It does not fire from empty cells and it does not override the Dashboard router.</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n"/>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="n"/>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="22" t="n"/>
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="23" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
